--- a/Model_zzy_RO/results_ro.xlsx
+++ b/Model_zzy_RO/results_ro.xlsx
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1225.022483592374</v>
+        <v>981.0840693566405</v>
       </c>
     </row>
     <row r="27">
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1247.310789323421</v>
+        <v>1028.469625769854</v>
       </c>
     </row>
     <row r="28">
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1185.437767352406</v>
+        <v>945.7398362049461</v>
       </c>
     </row>
     <row r="29">
@@ -717,7 +717,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1196.694625221943</v>
+        <v>972.9761114260581</v>
       </c>
     </row>
     <row r="30">
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1203.162878508475</v>
+        <v>971.2580590116795</v>
       </c>
     </row>
     <row r="31">
@@ -737,7 +737,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1405.315697509131</v>
+        <v>1188.039714314904</v>
       </c>
     </row>
     <row r="32">
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3097.436093719008</v>
+        <v>2863.110444415872</v>
       </c>
     </row>
     <row r="33">
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.717298791955727</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1823.825420044147</v>
+        <v>1274.52595967425</v>
       </c>
     </row>
     <row r="35">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1894.979917796183</v>
+        <v>1506.551695883818</v>
       </c>
     </row>
     <row r="36">
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1857.585695513623</v>
+        <v>1332.953035262953</v>
       </c>
     </row>
     <row r="37">
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1879.019634562442</v>
+        <v>1327.608750841566</v>
       </c>
     </row>
     <row r="38">
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1980.086305001832</v>
+        <v>1460.927830555015</v>
       </c>
     </row>
     <row r="39">
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1947.312599153839</v>
+        <v>1451.759137543859</v>
       </c>
     </row>
     <row r="40">
@@ -827,7 +827,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1966.066069277602</v>
+        <v>1421.48924783945</v>
       </c>
     </row>
     <row r="41">
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2297.183038923773</v>
+        <v>1856.874601276194</v>
       </c>
     </row>
     <row r="42">
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4152.23767668963</v>
+        <v>3795.467808746002</v>
       </c>
     </row>
     <row r="43">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>389.9916367388548</v>
+        <v>81.20772004514129</v>
       </c>
     </row>
     <row r="44">
@@ -867,7 +867,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2198.74272675017</v>
+        <v>1926.113004817459</v>
       </c>
     </row>
     <row r="45">
@@ -877,7 +877,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2148.182541991673</v>
+        <v>1893.283365621321</v>
       </c>
     </row>
     <row r="46">
@@ -887,7 +887,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2049.461005391525</v>
+        <v>1769.844086995368</v>
       </c>
     </row>
     <row r="47">
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2005.623346004106</v>
+        <v>1729.785436491433</v>
       </c>
     </row>
     <row r="48">
@@ -907,7 +907,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2034.52646369242</v>
+        <v>1810.18049990195</v>
       </c>
     </row>
     <row r="49">
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3512.955724381447</v>
+        <v>3263.09622225155</v>
       </c>
     </row>
     <row r="50">
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1.658492516348758</v>
+        <v>3.316985032697517</v>
       </c>
     </row>
     <row r="51">
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1.484833246118853</v>
+        <v>2.969666492237707</v>
       </c>
     </row>
     <row r="52">
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1.717904303451661</v>
+        <v>3.435808606903322</v>
       </c>
     </row>
     <row r="53">
@@ -957,7 +957,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1.999829633027502</v>
+        <v>3.999659266055005</v>
       </c>
     </row>
     <row r="54">
@@ -967,7 +967,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1.694473565420566</v>
+        <v>3.388947130841132</v>
       </c>
     </row>
     <row r="55">
@@ -977,7 +977,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1.325861354733888</v>
+        <v>2.651722709467776</v>
       </c>
     </row>
     <row r="56">
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.4867894410432996</v>
+        <v>0.9735788820865992</v>
       </c>
     </row>
     <row r="57">
@@ -997,7 +997,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.7069674464461286</v>
+        <v>1.413934892892257</v>
       </c>
     </row>
     <row r="58">
@@ -1007,7 +1007,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>41.78827083109428</v>
+        <v>83.57654166218856</v>
       </c>
     </row>
     <row r="59">
@@ -1017,7 +1017,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>120.741440560809</v>
+        <v>241.482881121618</v>
       </c>
     </row>
     <row r="60">
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>263.286967848858</v>
+        <v>526.5739356977159</v>
       </c>
     </row>
     <row r="61">
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>340.904299969851</v>
+        <v>681.808599939702</v>
       </c>
     </row>
     <row r="62">
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>339.060999670721</v>
+        <v>678.121999341442</v>
       </c>
     </row>
     <row r="63">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>274.127729288314</v>
+        <v>548.2554585766279</v>
       </c>
     </row>
     <row r="64">
@@ -1067,7 +1067,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>256.4350862078959</v>
+        <v>512.8701724157919</v>
       </c>
     </row>
     <row r="65">
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>154.289785638845</v>
+        <v>308.57957127769</v>
       </c>
     </row>
     <row r="66">
@@ -1087,7 +1087,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>70.29183247195209</v>
+        <v>140.5836649439041</v>
       </c>
     </row>
     <row r="67">
@@ -1097,7 +1097,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>8.641909429536838</v>
+        <v>17.28381885907368</v>
       </c>
     </row>
     <row r="68">
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>2.208903070853694</v>
+        <v>4.417806141707388</v>
       </c>
     </row>
     <row r="69">
@@ -1117,7 +1117,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1.409717306246534</v>
+        <v>2.819434612493069</v>
       </c>
     </row>
     <row r="70">
@@ -1127,7 +1127,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>2.044443103688707</v>
+        <v>4.088886207377413</v>
       </c>
     </row>
     <row r="71">
@@ -1137,7 +1137,7 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1.654886155957684</v>
+        <v>3.309772311915367</v>
       </c>
     </row>
     <row r="72">
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1.592343275163984</v>
+        <v>3.184686550327967</v>
       </c>
     </row>
     <row r="73">
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1.712910744546548</v>
+        <v>3.425821489093096</v>
       </c>
     </row>
     <row r="74">
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>258.167329998588</v>
+        <v>516.334659997176</v>
       </c>
     </row>
     <row r="75">
@@ -1177,7 +1177,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>233.470047086179</v>
+        <v>466.940094172358</v>
       </c>
     </row>
     <row r="76">
@@ -1187,7 +1187,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>253.685502330424</v>
+        <v>507.371004660848</v>
       </c>
     </row>
     <row r="77">
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>237.257741262225</v>
+        <v>474.51548252445</v>
       </c>
     </row>
     <row r="78">
@@ -1207,7 +1207,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>245.953564689587</v>
+        <v>491.907129379174</v>
       </c>
     </row>
     <row r="79">
@@ -1217,7 +1217,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>231.965063407281</v>
+        <v>463.930126814562</v>
       </c>
     </row>
     <row r="80">
@@ -1227,7 +1227,7 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>249.744985884758</v>
+        <v>499.489971769516</v>
       </c>
     </row>
     <row r="81">
@@ -1237,7 +1237,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>260.054735469737</v>
+        <v>520.109470939474</v>
       </c>
     </row>
     <row r="82">
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>281.757979063166</v>
+        <v>563.515958126332</v>
       </c>
     </row>
     <row r="83">
@@ -1257,7 +1257,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>285.105124959708</v>
+        <v>570.210249919416</v>
       </c>
     </row>
     <row r="84">
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>279.162035210718</v>
+        <v>558.324070421436</v>
       </c>
     </row>
     <row r="85">
@@ -1277,7 +1277,7 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>229.257217848332</v>
+        <v>458.514435696664</v>
       </c>
     </row>
     <row r="86">
@@ -1287,7 +1287,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>198.986030414947</v>
+        <v>397.972060829894</v>
       </c>
     </row>
     <row r="87">
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>240.322115559542</v>
+        <v>480.644231119084</v>
       </c>
     </row>
     <row r="88">
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>306.172382214635</v>
+        <v>612.34476442927</v>
       </c>
     </row>
     <row r="89">
@@ -1317,7 +1317,7 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>304.591121569898</v>
+        <v>609.182243139796</v>
       </c>
     </row>
     <row r="90">
@@ -1327,7 +1327,7 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>304.380898672297</v>
+        <v>608.761797344594</v>
       </c>
     </row>
     <row r="91">
@@ -1337,7 +1337,7 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>317.784537359451</v>
+        <v>635.569074718902</v>
       </c>
     </row>
     <row r="92">
@@ -1347,7 +1347,7 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>287.875866724259</v>
+        <v>575.7517334485181</v>
       </c>
     </row>
     <row r="93">
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>270.975620949514</v>
+        <v>541.951241899028</v>
       </c>
     </row>
     <row r="94">
@@ -1367,7 +1367,7 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>295.013166372296</v>
+        <v>590.026332744592</v>
       </c>
     </row>
     <row r="95">
@@ -1377,7 +1377,7 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>290.798723423796</v>
+        <v>581.597446847592</v>
       </c>
     </row>
     <row r="96">
@@ -1387,7 +1387,7 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>239.066748058282</v>
+        <v>478.133496116564</v>
       </c>
     </row>
     <row r="97">
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>263.840943870236</v>
+        <v>527.681887740472</v>
       </c>
     </row>
     <row r="98">
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>-1796.4</v>
+        <v>-1553.464737513222</v>
       </c>
     </row>
     <row r="106">
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0</v>
+        <v>-242.4493919618044</v>
       </c>
     </row>
     <row r="107">
@@ -1717,7 +1717,7 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0</v>
+        <v>269.9280694297534</v>
       </c>
     </row>
     <row r="130">
@@ -1737,7 +1737,7 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -1747,7 +1747,7 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
@@ -1757,7 +1757,7 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
@@ -1767,7 +1767,7 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="137">
@@ -1857,7 +1857,7 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161">
@@ -2197,7 +2197,7 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>1796.4</v>
+        <v>1553.464737513222</v>
       </c>
     </row>
     <row r="178">
@@ -2207,7 +2207,7 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>-0</v>
+        <v>242.4493919618044</v>
       </c>
     </row>
     <row r="179">
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="181">
@@ -2237,7 +2237,7 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="182">
@@ -2247,7 +2247,7 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="183">
@@ -2257,7 +2257,7 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="184">
@@ -2347,7 +2347,7 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="193">
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="B264" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
     </row>
     <row r="265">
@@ -5247,7 +5247,7 @@
         </is>
       </c>
       <c r="B482" t="n">
-        <v>52.95802759734534</v>
+        <v>68.84543587654889</v>
       </c>
     </row>
     <row r="483">
@@ -5257,7 +5257,7 @@
         </is>
       </c>
       <c r="B483" t="n">
-        <v>53.71238926243911</v>
+        <v>69.82610604117089</v>
       </c>
     </row>
     <row r="484">
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="B484" t="n">
-        <v>52.35158495472066</v>
+        <v>68.0570604411369</v>
       </c>
     </row>
     <row r="485">
@@ -5277,7 +5277,7 @@
         </is>
       </c>
       <c r="B485" t="n">
-        <v>51.79685699789111</v>
+        <v>67.33591409725845</v>
       </c>
     </row>
     <row r="486">
@@ -5287,7 +5287,7 @@
         </is>
       </c>
       <c r="B486" t="n">
-        <v>52.47739586070644</v>
+        <v>68.22061461891843</v>
       </c>
     </row>
     <row r="487">
@@ -5297,7 +5297,7 @@
         </is>
       </c>
       <c r="B487" t="n">
-        <v>53.38313855929245</v>
+        <v>69.39808012708022</v>
       </c>
     </row>
     <row r="488">
@@ -5307,7 +5307,7 @@
         </is>
       </c>
       <c r="B488" t="n">
-        <v>53.02042007555156</v>
+        <v>68.9265460982171</v>
       </c>
     </row>
     <row r="489">
@@ -5317,7 +5317,7 @@
         </is>
       </c>
       <c r="B489" t="n">
-        <v>53.69713879149867</v>
+        <v>69.80628042894823</v>
       </c>
     </row>
     <row r="490">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="B490" t="n">
-        <v>55.65393828722467</v>
+        <v>72.35011977339201</v>
       </c>
     </row>
     <row r="491">
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="B491" t="n">
-        <v>58.06114536050666</v>
+        <v>75.47948896865867</v>
       </c>
     </row>
     <row r="492">
@@ -5347,7 +5347,7 @@
         </is>
       </c>
       <c r="B492" t="n">
-        <v>59.38780936301888</v>
+        <v>77.20415217192445</v>
       </c>
     </row>
     <row r="493">
@@ -5357,7 +5357,7 @@
         </is>
       </c>
       <c r="B493" t="n">
-        <v>62.50211365769155</v>
+        <v>81.25274775499912</v>
       </c>
     </row>
     <row r="494">
@@ -5367,7 +5367,7 @@
         </is>
       </c>
       <c r="B494" t="n">
-        <v>62.96185212950267</v>
+        <v>81.85040776835356</v>
       </c>
     </row>
     <row r="495">
@@ -5377,7 +5377,7 @@
         </is>
       </c>
       <c r="B495" t="n">
-        <v>62.98794412625199</v>
+        <v>81.88432736412756</v>
       </c>
     </row>
     <row r="496">
@@ -5387,7 +5387,7 @@
         </is>
       </c>
       <c r="B496" t="n">
-        <v>60.10215661459443</v>
+        <v>78.13280359897266</v>
       </c>
     </row>
     <row r="497">
@@ -5397,7 +5397,7 @@
         </is>
       </c>
       <c r="B497" t="n">
-        <v>61.90823187055111</v>
+        <v>80.48070143171645</v>
       </c>
     </row>
     <row r="498">
@@ -5407,7 +5407,7 @@
         </is>
       </c>
       <c r="B498" t="n">
-        <v>59.67621066873668</v>
+        <v>77.57907386935777</v>
       </c>
     </row>
     <row r="499">
@@ -5417,7 +5417,7 @@
         </is>
       </c>
       <c r="B499" t="n">
-        <v>58.80843365091266</v>
+        <v>76.45096374618645</v>
       </c>
     </row>
     <row r="500">
@@ -5427,7 +5427,7 @@
         </is>
       </c>
       <c r="B500" t="n">
-        <v>58.18349287466999</v>
+        <v>75.63854073707111</v>
       </c>
     </row>
     <row r="501">
@@ -5437,7 +5437,7 @@
         </is>
       </c>
       <c r="B501" t="n">
-        <v>58.28720628469379</v>
+        <v>75.773368170102</v>
       </c>
     </row>
     <row r="502">
@@ -5447,7 +5447,7 @@
         </is>
       </c>
       <c r="B502" t="n">
-        <v>58.13563693275955</v>
+        <v>75.57632801258734</v>
       </c>
     </row>
     <row r="503">
@@ -5457,7 +5457,7 @@
         </is>
       </c>
       <c r="B503" t="n">
-        <v>55.38566689026712</v>
+        <v>72.00136695734733</v>
       </c>
     </row>
     <row r="504">
@@ -5467,7 +5467,7 @@
         </is>
       </c>
       <c r="B504" t="n">
-        <v>54.37709180992267</v>
+        <v>70.69021935289955</v>
       </c>
     </row>
     <row r="505">
@@ -5477,7 +5477,7 @@
         </is>
       </c>
       <c r="B505" t="n">
-        <v>52.31450828294845</v>
+        <v>68.0088607678329</v>
       </c>
     </row>
     <row r="506">
@@ -5487,7 +5487,7 @@
         </is>
       </c>
       <c r="B506" t="n">
-        <v>52.95802759734534</v>
+        <v>68.84543587654889</v>
       </c>
     </row>
     <row r="507">
@@ -5497,7 +5497,7 @@
         </is>
       </c>
       <c r="B507" t="n">
-        <v>53.71238926243911</v>
+        <v>69.82610604117089</v>
       </c>
     </row>
     <row r="508">
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="B508" t="n">
-        <v>52.35158495472066</v>
+        <v>68.0570604411369</v>
       </c>
     </row>
     <row r="509">
@@ -5517,7 +5517,7 @@
         </is>
       </c>
       <c r="B509" t="n">
-        <v>51.79685699789111</v>
+        <v>67.33591409725845</v>
       </c>
     </row>
     <row r="510">
@@ -5527,7 +5527,7 @@
         </is>
       </c>
       <c r="B510" t="n">
-        <v>52.47739586070644</v>
+        <v>68.22061461891843</v>
       </c>
     </row>
     <row r="511">
@@ -5537,7 +5537,7 @@
         </is>
       </c>
       <c r="B511" t="n">
-        <v>53.38313855929245</v>
+        <v>69.39808012708022</v>
       </c>
     </row>
     <row r="512">
@@ -5547,7 +5547,7 @@
         </is>
       </c>
       <c r="B512" t="n">
-        <v>53.02042007555156</v>
+        <v>68.9265460982171</v>
       </c>
     </row>
     <row r="513">
@@ -5557,7 +5557,7 @@
         </is>
       </c>
       <c r="B513" t="n">
-        <v>53.69713879149867</v>
+        <v>69.80628042894823</v>
       </c>
     </row>
     <row r="514">
@@ -5567,7 +5567,7 @@
         </is>
       </c>
       <c r="B514" t="n">
-        <v>55.65393828722467</v>
+        <v>72.35011977339201</v>
       </c>
     </row>
     <row r="515">
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="B515" t="n">
-        <v>58.06114536050666</v>
+        <v>75.47948896865867</v>
       </c>
     </row>
     <row r="516">
@@ -5587,7 +5587,7 @@
         </is>
       </c>
       <c r="B516" t="n">
-        <v>59.38780936301888</v>
+        <v>77.20415217192445</v>
       </c>
     </row>
     <row r="517">
@@ -5597,7 +5597,7 @@
         </is>
       </c>
       <c r="B517" t="n">
-        <v>62.50211365769155</v>
+        <v>81.25274775499912</v>
       </c>
     </row>
     <row r="518">
@@ -5607,7 +5607,7 @@
         </is>
       </c>
       <c r="B518" t="n">
-        <v>62.96185212950267</v>
+        <v>81.85040776835356</v>
       </c>
     </row>
     <row r="519">
@@ -5617,7 +5617,7 @@
         </is>
       </c>
       <c r="B519" t="n">
-        <v>62.98794412625199</v>
+        <v>81.88432736412756</v>
       </c>
     </row>
     <row r="520">
@@ -5627,7 +5627,7 @@
         </is>
       </c>
       <c r="B520" t="n">
-        <v>60.10215661459443</v>
+        <v>78.13280359897266</v>
       </c>
     </row>
     <row r="521">
@@ -5637,7 +5637,7 @@
         </is>
       </c>
       <c r="B521" t="n">
-        <v>61.90823187055111</v>
+        <v>80.48070143171645</v>
       </c>
     </row>
     <row r="522">
@@ -5647,7 +5647,7 @@
         </is>
       </c>
       <c r="B522" t="n">
-        <v>59.67621066873668</v>
+        <v>77.57907386935777</v>
       </c>
     </row>
     <row r="523">
@@ -5657,7 +5657,7 @@
         </is>
       </c>
       <c r="B523" t="n">
-        <v>58.80843365091266</v>
+        <v>76.45096374618645</v>
       </c>
     </row>
     <row r="524">
@@ -5667,7 +5667,7 @@
         </is>
       </c>
       <c r="B524" t="n">
-        <v>58.18349287466999</v>
+        <v>75.63854073707111</v>
       </c>
     </row>
     <row r="525">
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="B525" t="n">
-        <v>58.28720628469379</v>
+        <v>75.773368170102</v>
       </c>
     </row>
     <row r="526">
@@ -5687,7 +5687,7 @@
         </is>
       </c>
       <c r="B526" t="n">
-        <v>58.13563693275955</v>
+        <v>75.57632801258734</v>
       </c>
     </row>
     <row r="527">
@@ -5697,7 +5697,7 @@
         </is>
       </c>
       <c r="B527" t="n">
-        <v>55.38566689026712</v>
+        <v>72.00136695734733</v>
       </c>
     </row>
     <row r="528">
@@ -5707,7 +5707,7 @@
         </is>
       </c>
       <c r="B528" t="n">
-        <v>54.37709180992267</v>
+        <v>70.69021935289955</v>
       </c>
     </row>
     <row r="529">
@@ -5717,7 +5717,7 @@
         </is>
       </c>
       <c r="B529" t="n">
-        <v>52.31450828294845</v>
+        <v>68.0088607678329</v>
       </c>
     </row>
     <row r="530">
@@ -7267,7 +7267,7 @@
         </is>
       </c>
       <c r="B684" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="685">
@@ -7277,7 +7277,7 @@
         </is>
       </c>
       <c r="B685" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="686">
@@ -7297,7 +7297,7 @@
         </is>
       </c>
       <c r="B687" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="688">
@@ -7307,7 +7307,7 @@
         </is>
       </c>
       <c r="B688" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="689">
@@ -7367,7 +7367,7 @@
         </is>
       </c>
       <c r="B694" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="695">
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="B696" t="n">
-        <v>6.550468809046198</v>
+        <v>6.350468809046198</v>
       </c>
     </row>
     <row r="697">
@@ -7487,7 +7487,7 @@
         </is>
       </c>
       <c r="B706" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="707">
@@ -7497,7 +7497,7 @@
         </is>
       </c>
       <c r="B707" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="708">
@@ -7507,7 +7507,7 @@
         </is>
       </c>
       <c r="B708" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="709">
@@ -7517,7 +7517,7 @@
         </is>
       </c>
       <c r="B709" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="710">
@@ -7537,7 +7537,7 @@
         </is>
       </c>
       <c r="B711" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="712">
@@ -9547,7 +9547,7 @@
         </is>
       </c>
       <c r="B912" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="913">
@@ -10027,7 +10027,7 @@
         </is>
       </c>
       <c r="B960" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="961">
@@ -14127,7 +14127,7 @@
         </is>
       </c>
       <c r="B1370" t="n">
-        <v>132.7642184415284</v>
+        <v>242.1069695395764</v>
       </c>
     </row>
     <row r="1371">
@@ -14137,7 +14137,7 @@
         </is>
       </c>
       <c r="B1371" t="n">
-        <v>86.46851243702041</v>
+        <v>197.3687985024096</v>
       </c>
     </row>
     <row r="1372">
@@ -14147,7 +14147,7 @@
         </is>
       </c>
       <c r="B1372" t="n">
-        <v>79.56876683579227</v>
+        <v>187.6593922423041</v>
       </c>
     </row>
     <row r="1373">
@@ -14157,7 +14157,7 @@
         </is>
       </c>
       <c r="B1373" t="n">
-        <v>127.174268743304</v>
+        <v>234.1195440742439</v>
       </c>
     </row>
     <row r="1374">
@@ -14167,7 +14167,7 @@
         </is>
       </c>
       <c r="B1374" t="n">
-        <v>146.0540942009958</v>
+        <v>254.4044821251607</v>
       </c>
     </row>
     <row r="1375">
@@ -14177,7 +14177,7 @@
         </is>
       </c>
       <c r="B1375" t="n">
-        <v>144.0509634888549</v>
+        <v>254.2714436906884</v>
       </c>
     </row>
     <row r="1376">
@@ -14187,7 +14187,7 @@
         </is>
       </c>
       <c r="B1376" t="n">
-        <v>154.90727766283</v>
+        <v>264.3788508776458</v>
       </c>
     </row>
     <row r="1377">
@@ -14197,7 +14197,7 @@
         </is>
       </c>
       <c r="B1377" t="n">
-        <v>80.3861139601386</v>
+        <v>191.254912288468</v>
       </c>
     </row>
     <row r="1378">
@@ -14207,7 +14207,7 @@
         </is>
       </c>
       <c r="B1378" t="n">
-        <v>137.2441132204886</v>
+        <v>252.1531269782285</v>
       </c>
     </row>
     <row r="1379">
@@ -14217,7 +14217,7 @@
         </is>
       </c>
       <c r="B1379" t="n">
-        <v>101.4282086205067</v>
+        <v>221.3073969824941</v>
       </c>
     </row>
     <row r="1380">
@@ -14227,7 +14227,7 @@
         </is>
       </c>
       <c r="B1380" t="n">
-        <v>72.62094665300502</v>
+        <v>195.2393059848845</v>
       </c>
     </row>
     <row r="1381">
@@ -14237,7 +14237,7 @@
         </is>
       </c>
       <c r="B1381" t="n">
-        <v>6.354010718733003</v>
+        <v>135.4024924472616</v>
       </c>
     </row>
     <row r="1382">
@@ -14247,7 +14247,7 @@
         </is>
       </c>
       <c r="B1382" t="n">
-        <v>-0</v>
+        <v>50.14256649852786</v>
       </c>
     </row>
     <row r="1383">
@@ -14257,7 +14257,7 @@
         </is>
       </c>
       <c r="B1383" t="n">
-        <v>0</v>
+        <v>112.8950860044672</v>
       </c>
     </row>
     <row r="1384">
@@ -14267,7 +14267,7 @@
         </is>
       </c>
       <c r="B1384" t="n">
-        <v>90.11121941857247</v>
+        <v>214.2044957228226</v>
       </c>
     </row>
     <row r="1385">
@@ -14277,7 +14277,7 @@
         </is>
       </c>
       <c r="B1385" t="n">
-        <v>0</v>
+        <v>23.51537523687421</v>
       </c>
     </row>
     <row r="1386">
@@ -14287,7 +14287,7 @@
         </is>
       </c>
       <c r="B1386" t="n">
-        <v>42.79673562141262</v>
+        <v>115.2659202406353</v>
       </c>
     </row>
     <row r="1387">
@@ -14297,7 +14297,7 @@
         </is>
       </c>
       <c r="B1387" t="n">
-        <v>94.5929918795384</v>
+        <v>129.6607674774424</v>
       </c>
     </row>
     <row r="1388">
@@ -14307,7 +14307,7 @@
         </is>
       </c>
       <c r="B1388" t="n">
-        <v>129.9020259269032</v>
+        <v>71.59312162029704</v>
       </c>
     </row>
     <row r="1389">
@@ -14317,7 +14317,7 @@
         </is>
       </c>
       <c r="B1389" t="n">
-        <v>119.3496981428109</v>
+        <v>129.6667578548063</v>
       </c>
     </row>
     <row r="1390">
@@ -14327,7 +14327,7 @@
         </is>
       </c>
       <c r="B1390" t="n">
-        <v>50.90776824737627</v>
+        <v>170.9407597967793</v>
       </c>
     </row>
     <row r="1391">
@@ -14337,7 +14337,7 @@
         </is>
       </c>
       <c r="B1391" t="n">
-        <v>-0</v>
+        <v>109.5592259132853</v>
       </c>
     </row>
     <row r="1392">
@@ -14347,7 +14347,7 @@
         </is>
       </c>
       <c r="B1392" t="n">
-        <v>203.5066490468288</v>
+        <v>71.86985270849902</v>
       </c>
     </row>
     <row r="1393">
@@ -14367,7 +14367,7 @@
         </is>
       </c>
       <c r="B1394" t="n">
-        <v>67.9774026027556</v>
+        <v>405.7509718721734</v>
       </c>
     </row>
     <row r="1395">
@@ -14377,7 +14377,7 @@
         </is>
       </c>
       <c r="B1395" t="n">
-        <v>-0</v>
+        <v>282.1833555306389</v>
       </c>
     </row>
     <row r="1396">
@@ -14387,7 +14387,7 @@
         </is>
       </c>
       <c r="B1396" t="n">
-        <v>66.35826195737113</v>
+        <v>398.3826905814095</v>
       </c>
     </row>
     <row r="1397">
@@ -14397,7 +14397,7 @@
         </is>
       </c>
       <c r="B1397" t="n">
-        <v>70.49917549716113</v>
+        <v>381.5340176609894</v>
       </c>
     </row>
     <row r="1398">
@@ -14407,7 +14407,7 @@
         </is>
       </c>
       <c r="B1398" t="n">
-        <v>327.3049497315073</v>
+        <v>649.2473994630172</v>
       </c>
     </row>
     <row r="1399">
@@ -14417,7 +14417,7 @@
         </is>
       </c>
       <c r="B1399" t="n">
-        <v>322.8242021906219</v>
+        <v>626.1024043812411</v>
       </c>
     </row>
     <row r="1400">
@@ -14427,7 +14427,7 @@
         </is>
       </c>
       <c r="B1400" t="n">
-        <v>618.172974590204</v>
+        <v>943.4742825137457</v>
       </c>
     </row>
     <row r="1401">
@@ -14437,7 +14437,7 @@
         </is>
       </c>
       <c r="B1401" t="n">
-        <v>245.7718804577024</v>
+        <v>584.7620942487404</v>
       </c>
     </row>
     <row r="1402">
@@ -14447,7 +14447,7 @@
         </is>
       </c>
       <c r="B1402" t="n">
-        <v>383.5509581958713</v>
+        <v>804.1610830584096</v>
       </c>
     </row>
     <row r="1403">
@@ -14457,7 +14457,7 @@
         </is>
       </c>
       <c r="B1403" t="n">
-        <v>358.1352018433337</v>
+        <v>885.7357370200058</v>
       </c>
     </row>
     <row r="1404">
@@ -14467,7 +14467,7 @@
         </is>
       </c>
       <c r="B1404" t="n">
-        <v>339.7033706441127</v>
+        <v>1044.887074621561</v>
       </c>
     </row>
     <row r="1405">
@@ -14477,7 +14477,7 @@
         </is>
       </c>
       <c r="B1405" t="n">
-        <v>419.7399731636358</v>
+        <v>1160.949946327274</v>
       </c>
     </row>
     <row r="1406">
@@ -14487,7 +14487,7 @@
         </is>
       </c>
       <c r="B1406" t="n">
-        <v>151.3675960091651</v>
+        <v>893.2517782227392</v>
       </c>
     </row>
     <row r="1407">
@@ -14497,7 +14497,7 @@
         </is>
       </c>
       <c r="B1407" t="n">
-        <v>296.144078195265</v>
+        <v>974.0432632710872</v>
       </c>
     </row>
     <row r="1408">
@@ -14507,7 +14507,7 @@
         </is>
       </c>
       <c r="B1408" t="n">
-        <v>264.5893756159616</v>
+        <v>995.9790845652518</v>
       </c>
     </row>
     <row r="1409">
@@ -14517,7 +14517,7 @@
         </is>
       </c>
       <c r="B1409" t="n">
-        <v>117.5344639662776</v>
+        <v>769.4926920760649</v>
       </c>
     </row>
     <row r="1410">
@@ -14527,7 +14527,7 @@
         </is>
       </c>
       <c r="B1410" t="n">
-        <v>-0</v>
+        <v>491.7047676417094</v>
       </c>
     </row>
     <row r="1411">
@@ -14537,7 +14537,7 @@
         </is>
       </c>
       <c r="B1411" t="n">
-        <v>-0</v>
+        <v>309.0754283180329</v>
       </c>
     </row>
     <row r="1412">
@@ -14547,7 +14547,7 @@
         </is>
       </c>
       <c r="B1412" t="n">
-        <v>-0</v>
+        <v>198.4285681339553</v>
       </c>
     </row>
     <row r="1413">
@@ -14557,7 +14557,7 @@
         </is>
       </c>
       <c r="B1413" t="n">
-        <v>-0</v>
+        <v>183.500379464977</v>
       </c>
     </row>
     <row r="1414">
@@ -14567,7 +14567,7 @@
         </is>
       </c>
       <c r="B1414" t="n">
-        <v>0</v>
+        <v>260.3939513042313</v>
       </c>
     </row>
     <row r="1415">
@@ -14577,7 +14577,7 @@
         </is>
       </c>
       <c r="B1415" t="n">
-        <v>-0</v>
+        <v>341.819718240686</v>
       </c>
     </row>
     <row r="1416">
@@ -14587,7 +14587,7 @@
         </is>
       </c>
       <c r="B1416" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="1417">
@@ -14607,7 +14607,7 @@
         </is>
       </c>
       <c r="B1418" t="n">
-        <v>112.8495856752992</v>
+        <v>205.79092410864</v>
       </c>
     </row>
     <row r="1419">
@@ -14617,7 +14617,7 @@
         </is>
       </c>
       <c r="B1419" t="n">
-        <v>73.49823557146735</v>
+        <v>167.7634787270482</v>
       </c>
     </row>
     <row r="1420">
@@ -14627,7 +14627,7 @@
         </is>
       </c>
       <c r="B1420" t="n">
-        <v>67.63345181042344</v>
+        <v>159.5104834059584</v>
       </c>
     </row>
     <row r="1421">
@@ -14637,7 +14637,7 @@
         </is>
       </c>
       <c r="B1421" t="n">
-        <v>108.0981284318084</v>
+        <v>199.0016124631073</v>
       </c>
     </row>
     <row r="1422">
@@ -14647,7 +14647,7 @@
         </is>
       </c>
       <c r="B1422" t="n">
-        <v>124.1459800708464</v>
+        <v>216.2438098063866</v>
       </c>
     </row>
     <row r="1423">
@@ -14657,7 +14657,7 @@
         </is>
       </c>
       <c r="B1423" t="n">
-        <v>122.4433189655267</v>
+        <v>216.1307271370852</v>
       </c>
     </row>
     <row r="1424">
@@ -14667,7 +14667,7 @@
         </is>
       </c>
       <c r="B1424" t="n">
-        <v>131.6711860134055</v>
+        <v>224.722023245999</v>
       </c>
     </row>
     <row r="1425">
@@ -14677,7 +14677,7 @@
         </is>
       </c>
       <c r="B1425" t="n">
-        <v>68.32819686611781</v>
+        <v>162.5666754451978</v>
       </c>
     </row>
     <row r="1426">
@@ -14687,7 +14687,7 @@
         </is>
       </c>
       <c r="B1426" t="n">
-        <v>116.6574962374153</v>
+        <v>214.3301579314942</v>
       </c>
     </row>
     <row r="1427">
@@ -14697,7 +14697,7 @@
         </is>
       </c>
       <c r="B1427" t="n">
-        <v>86.21397732743067</v>
+        <v>188.11128743512</v>
       </c>
     </row>
     <row r="1428">
@@ -14707,7 +14707,7 @@
         </is>
       </c>
       <c r="B1428" t="n">
-        <v>61.72780465505426</v>
+        <v>165.9534100871518</v>
       </c>
     </row>
     <row r="1429">
@@ -14717,7 +14717,7 @@
         </is>
       </c>
       <c r="B1429" t="n">
-        <v>5.400909110923052</v>
+        <v>115.0921185801724</v>
       </c>
     </row>
     <row r="1430">
@@ -14727,7 +14727,7 @@
         </is>
       </c>
       <c r="B1430" t="n">
-        <v>0</v>
+        <v>42.62118152374867</v>
       </c>
     </row>
     <row r="1431">
@@ -14737,7 +14737,7 @@
         </is>
       </c>
       <c r="B1431" t="n">
-        <v>0</v>
+        <v>95.96082310379714</v>
       </c>
     </row>
     <row r="1432">
@@ -14747,7 +14747,7 @@
         </is>
       </c>
       <c r="B1432" t="n">
-        <v>76.59453650578661</v>
+        <v>182.0738213643992</v>
       </c>
     </row>
     <row r="1433">
@@ -14757,7 +14757,7 @@
         </is>
       </c>
       <c r="B1433" t="n">
-        <v>0</v>
+        <v>19.98806895134308</v>
       </c>
     </row>
     <row r="1434">
@@ -14767,7 +14767,7 @@
         </is>
       </c>
       <c r="B1434" t="n">
-        <v>36.37722527820073</v>
+        <v>97.97603220453999</v>
       </c>
     </row>
     <row r="1435">
@@ -14777,7 +14777,7 @@
         </is>
       </c>
       <c r="B1435" t="n">
-        <v>80.40404309760764</v>
+        <v>110.211652355826</v>
       </c>
     </row>
     <row r="1436">
@@ -14787,7 +14787,7 @@
         </is>
       </c>
       <c r="B1436" t="n">
-        <v>110.4167220378677</v>
+        <v>60.85415337725248</v>
       </c>
     </row>
     <row r="1437">
@@ -14797,7 +14797,7 @@
         </is>
       </c>
       <c r="B1437" t="n">
-        <v>101.4472434213892</v>
+        <v>110.2167441765854</v>
       </c>
     </row>
     <row r="1438">
@@ -14807,7 +14807,7 @@
         </is>
       </c>
       <c r="B1438" t="n">
-        <v>43.27160301026983</v>
+        <v>145.2996458272624</v>
       </c>
     </row>
     <row r="1439">
@@ -14817,7 +14817,7 @@
         </is>
       </c>
       <c r="B1439" t="n">
-        <v>0</v>
+        <v>93.12534202629254</v>
       </c>
     </row>
     <row r="1440">
@@ -14827,7 +14827,7 @@
         </is>
       </c>
       <c r="B1440" t="n">
-        <v>172.9806516898045</v>
+        <v>61.08937480222417</v>
       </c>
     </row>
     <row r="1441">
@@ -14847,7 +14847,7 @@
         </is>
       </c>
       <c r="B1442" t="n">
-        <v>57.78079221234226</v>
+        <v>344.8883260913474</v>
       </c>
     </row>
     <row r="1443">
@@ -14857,7 +14857,7 @@
         </is>
       </c>
       <c r="B1443" t="n">
-        <v>0</v>
+        <v>239.8558522010431</v>
       </c>
     </row>
     <row r="1444">
@@ -14867,7 +14867,7 @@
         </is>
       </c>
       <c r="B1444" t="n">
-        <v>56.40452266376546</v>
+        <v>338.625286994198</v>
       </c>
     </row>
     <row r="1445">
@@ -14877,7 +14877,7 @@
         </is>
       </c>
       <c r="B1445" t="n">
-        <v>59.92429917258696</v>
+        <v>324.303915011841</v>
       </c>
     </row>
     <row r="1446">
@@ -14887,7 +14887,7 @@
         </is>
       </c>
       <c r="B1446" t="n">
-        <v>278.2092072717812</v>
+        <v>551.8602895435646</v>
       </c>
     </row>
     <row r="1447">
@@ -14897,7 +14897,7 @@
         </is>
       </c>
       <c r="B1447" t="n">
-        <v>274.4005718620286</v>
+        <v>532.1870437240549</v>
       </c>
     </row>
     <row r="1448">
@@ -14907,7 +14907,7 @@
         </is>
       </c>
       <c r="B1448" t="n">
-        <v>525.4470284016734</v>
+        <v>801.9531401366838</v>
       </c>
     </row>
     <row r="1449">
@@ -14917,7 +14917,7 @@
         </is>
       </c>
       <c r="B1449" t="n">
-        <v>208.906098389047</v>
+        <v>497.0477801114293</v>
       </c>
     </row>
     <row r="1450">
@@ -14927,7 +14927,7 @@
         </is>
       </c>
       <c r="B1450" t="n">
-        <v>326.0183144664906</v>
+        <v>683.5369205996482</v>
       </c>
     </row>
     <row r="1451">
@@ -14937,7 +14937,7 @@
         </is>
       </c>
       <c r="B1451" t="n">
-        <v>304.4149215668336</v>
+        <v>752.8753764670049</v>
       </c>
     </row>
     <row r="1452">
@@ -14947,7 +14947,7 @@
         </is>
       </c>
       <c r="B1452" t="n">
-        <v>288.7478650474958</v>
+        <v>888.1540134283272</v>
       </c>
     </row>
     <row r="1453">
@@ -14957,7 +14957,7 @@
         </is>
       </c>
       <c r="B1453" t="n">
-        <v>356.7789771890904</v>
+        <v>986.8074543781828</v>
       </c>
     </row>
     <row r="1454">
@@ -14967,7 +14967,7 @@
         </is>
       </c>
       <c r="B1454" t="n">
-        <v>128.6624566077903</v>
+        <v>759.2640114893283</v>
       </c>
     </row>
     <row r="1455">
@@ -14977,7 +14977,7 @@
         </is>
       </c>
       <c r="B1455" t="n">
-        <v>251.7224664659753</v>
+        <v>827.9367737804241</v>
       </c>
     </row>
     <row r="1456">
@@ -14987,7 +14987,7 @@
         </is>
       </c>
       <c r="B1456" t="n">
-        <v>224.9009692735673</v>
+        <v>846.582221880464</v>
       </c>
     </row>
     <row r="1457">
@@ -14997,7 +14997,7 @@
         </is>
       </c>
       <c r="B1457" t="n">
-        <v>99.90429437133595</v>
+        <v>654.0687882646552</v>
       </c>
     </row>
     <row r="1458">
@@ -15007,7 +15007,7 @@
         </is>
       </c>
       <c r="B1458" t="n">
-        <v>0</v>
+        <v>417.949052495453</v>
       </c>
     </row>
     <row r="1459">
@@ -15017,7 +15017,7 @@
         </is>
       </c>
       <c r="B1459" t="n">
-        <v>0</v>
+        <v>262.7141140703279</v>
       </c>
     </row>
     <row r="1460">
@@ -15027,7 +15027,7 @@
         </is>
       </c>
       <c r="B1460" t="n">
-        <v>0</v>
+        <v>168.664282913862</v>
       </c>
     </row>
     <row r="1461">
@@ -15037,7 +15037,7 @@
         </is>
       </c>
       <c r="B1461" t="n">
-        <v>0</v>
+        <v>155.9753225452304</v>
       </c>
     </row>
     <row r="1462">
@@ -15047,7 +15047,7 @@
         </is>
       </c>
       <c r="B1462" t="n">
-        <v>0</v>
+        <v>221.3348586085966</v>
       </c>
     </row>
     <row r="1463">
@@ -15057,7 +15057,7 @@
         </is>
       </c>
       <c r="B1463" t="n">
-        <v>0</v>
+        <v>290.5467605045831</v>
       </c>
     </row>
     <row r="1464">
@@ -15807,7 +15807,7 @@
         </is>
       </c>
       <c r="B1538" t="n">
-        <v>820.4767906650484</v>
+        <v>731.1101190945284</v>
       </c>
     </row>
     <row r="1539">
@@ -15817,7 +15817,7 @@
         </is>
       </c>
       <c r="B1539" t="n">
-        <v>829.1241646372282</v>
+        <v>738.4845077568621</v>
       </c>
     </row>
     <row r="1540">
@@ -15827,7 +15827,7 @@
         </is>
       </c>
       <c r="B1540" t="n">
-        <v>822.771951558061</v>
+        <v>734.4286519469696</v>
       </c>
     </row>
     <row r="1541">
@@ -15837,7 +15837,7 @@
         </is>
       </c>
       <c r="B1541" t="n">
-        <v>791.8500667372264</v>
+        <v>704.442870553285</v>
       </c>
     </row>
     <row r="1542">
@@ -15847,7 +15847,7 @@
         </is>
       </c>
       <c r="B1542" t="n">
-        <v>808.7503684507205</v>
+        <v>720.194762935778</v>
       </c>
     </row>
     <row r="1543">
@@ -15857,7 +15857,7 @@
         </is>
       </c>
       <c r="B1543" t="n">
-        <v>869.5437392737538</v>
+        <v>779.4596929549475</v>
       </c>
     </row>
     <row r="1544">
@@ -15867,7 +15867,7 @@
         </is>
       </c>
       <c r="B1544" t="n">
-        <v>878.9440948359228</v>
+        <v>789.472135958429</v>
       </c>
     </row>
     <row r="1545">
@@ -15877,7 +15877,7 @@
         </is>
       </c>
       <c r="B1545" t="n">
-        <v>1006.826840910537</v>
+        <v>916.2129191998828</v>
       </c>
     </row>
     <row r="1546">
@@ -15887,7 +15887,7 @@
         </is>
       </c>
       <c r="B1546" t="n">
-        <v>987.1810173075479</v>
+        <v>893.2649964478567</v>
       </c>
     </row>
     <row r="1547">
@@ -15897,7 +15897,7 @@
         </is>
       </c>
       <c r="B1547" t="n">
-        <v>1049.423013556942</v>
+        <v>951.4448307610867</v>
       </c>
     </row>
     <row r="1548">
@@ -15907,7 +15907,7 @@
         </is>
       </c>
       <c r="B1548" t="n">
-        <v>1123.771311022668</v>
+        <v>1023.554382722574</v>
       </c>
     </row>
     <row r="1549">
@@ -15917,7 +15917,7 @@
         </is>
       </c>
       <c r="B1549" t="n">
-        <v>1153.619704349831</v>
+        <v>1048.147387552476</v>
       </c>
     </row>
     <row r="1550">
@@ -15927,7 +15927,7 @@
         </is>
       </c>
       <c r="B1550" t="n">
-        <v>1147.912587838805</v>
+        <v>1041.664462370269</v>
       </c>
     </row>
     <row r="1551">
@@ -15937,7 +15937,7 @@
         </is>
       </c>
       <c r="B1551" t="n">
-        <v>1061.165899591316</v>
+        <v>954.8737438782664</v>
       </c>
     </row>
     <row r="1552">
@@ -15947,7 +15947,7 @@
         </is>
       </c>
       <c r="B1552" t="n">
-        <v>1113.148765147844</v>
+        <v>1011.726375860716</v>
       </c>
     </row>
     <row r="1553">
@@ -15957,7 +15957,7 @@
         </is>
       </c>
       <c r="B1553" t="n">
-        <v>1161.675913984164</v>
+        <v>1057.205772702609</v>
       </c>
     </row>
     <row r="1554">
@@ -15967,7 +15967,7 @@
         </is>
       </c>
       <c r="B1554" t="n">
-        <v>1071.306951912573</v>
+        <v>970.6033464090793</v>
       </c>
     </row>
     <row r="1555">
@@ -15977,7 +15977,7 @@
         </is>
       </c>
       <c r="B1555" t="n">
-        <v>1101.342039756747</v>
+        <v>1002.102807970832</v>
       </c>
     </row>
     <row r="1556">
@@ -15987,7 +15987,7 @@
         </is>
       </c>
       <c r="B1556" t="n">
-        <v>1131.185912296069</v>
+        <v>1033.001268070062</v>
       </c>
     </row>
     <row r="1557">
@@ -15997,7 +15997,7 @@
         </is>
       </c>
       <c r="B1557" t="n">
-        <v>1058.496470799448</v>
+        <v>960.1368101940268</v>
       </c>
     </row>
     <row r="1558">
@@ -16007,7 +16007,7 @@
         </is>
       </c>
       <c r="B1558" t="n">
-        <v>1027.598388842531</v>
+        <v>929.4945015184994</v>
       </c>
     </row>
     <row r="1559">
@@ -16017,7 +16017,7 @@
         </is>
       </c>
       <c r="B1559" t="n">
-        <v>1057.78669333867</v>
+        <v>964.3233804613436</v>
       </c>
     </row>
     <row r="1560">
@@ -16027,7 +16027,7 @@
         </is>
       </c>
       <c r="B1560" t="n">
-        <v>1004.550937378968</v>
+        <v>912.7895949497233</v>
       </c>
     </row>
     <row r="1561">
@@ -16037,7 +16037,7 @@
         </is>
       </c>
       <c r="B1561" t="n">
-        <v>1396.852271782154</v>
+        <v>1308.571539054679</v>
       </c>
     </row>
     <row r="1562">
@@ -16287,7 +16287,7 @@
         </is>
       </c>
       <c r="B1586" t="n">
-        <v>474.5945938517194</v>
+        <v>385.2279222811994</v>
       </c>
     </row>
     <row r="1587">
@@ -16297,7 +16297,7 @@
         </is>
       </c>
       <c r="B1587" t="n">
-        <v>479.7372757005775</v>
+        <v>389.0976188202113</v>
       </c>
     </row>
     <row r="1588">
@@ -16307,7 +16307,7 @@
         </is>
       </c>
       <c r="B1588" t="n">
-        <v>485.218893496473</v>
+        <v>396.8755938853816</v>
       </c>
     </row>
     <row r="1589">
@@ -16317,7 +16317,7 @@
         </is>
       </c>
       <c r="B1589" t="n">
-        <v>457.2274253920102</v>
+        <v>369.8202292080688</v>
       </c>
     </row>
     <row r="1590">
@@ -16327,7 +16327,7 @@
         </is>
       </c>
       <c r="B1590" t="n">
-        <v>486.9298022703892</v>
+        <v>398.3741967554467</v>
       </c>
     </row>
     <row r="1591">
@@ -16337,7 +16337,7 @@
         </is>
       </c>
       <c r="B1591" t="n">
-        <v>484.7730094320891</v>
+        <v>394.6889631132829</v>
       </c>
     </row>
     <row r="1592">
@@ -16347,7 +16347,7 @@
         </is>
       </c>
       <c r="B1592" t="n">
-        <v>482.2276430235987</v>
+        <v>392.755684146105</v>
       </c>
     </row>
     <row r="1593">
@@ -16357,7 +16357,7 @@
         </is>
       </c>
       <c r="B1593" t="n">
-        <v>488.1188252822096</v>
+        <v>397.5049035715558</v>
       </c>
     </row>
     <row r="1594">
@@ -16367,7 +16367,7 @@
         </is>
       </c>
       <c r="B1594" t="n">
-        <v>495.6579322510516</v>
+        <v>401.7419113913604</v>
       </c>
     </row>
     <row r="1595">
@@ -16377,7 +16377,7 @@
         </is>
       </c>
       <c r="B1595" t="n">
-        <v>524.1518150196667</v>
+        <v>426.1736322238116</v>
       </c>
     </row>
     <row r="1596">
@@ -16387,7 +16387,7 @@
         </is>
       </c>
       <c r="B1596" t="n">
-        <v>570.1177242817644</v>
+        <v>469.9007959816706</v>
       </c>
     </row>
     <row r="1597">
@@ -16397,7 +16397,7 @@
         </is>
       </c>
       <c r="B1597" t="n">
-        <v>571.4318652181396</v>
+        <v>465.9595484207845</v>
       </c>
     </row>
     <row r="1598">
@@ -16407,7 +16407,7 @@
         </is>
       </c>
       <c r="B1598" t="n">
-        <v>529.5740795216229</v>
+        <v>423.3259540530866</v>
       </c>
     </row>
     <row r="1599">
@@ -16417,7 +16417,7 @@
         </is>
       </c>
       <c r="B1599" t="n">
-        <v>511.9114183276154</v>
+        <v>405.6192626145653</v>
       </c>
     </row>
     <row r="1600">
@@ -16427,7 +16427,7 @@
         </is>
       </c>
       <c r="B1600" t="n">
-        <v>547.1298318884034</v>
+        <v>445.7074426012758</v>
       </c>
     </row>
     <row r="1601">
@@ -16437,7 +16437,7 @@
         </is>
       </c>
       <c r="B1601" t="n">
-        <v>531.8617494670865</v>
+        <v>427.3916081855314</v>
       </c>
     </row>
     <row r="1602">
@@ -16447,7 +16447,7 @@
         </is>
       </c>
       <c r="B1602" t="n">
-        <v>493.2742887454199</v>
+        <v>392.5706832419263</v>
       </c>
     </row>
     <row r="1603">
@@ -16457,7 +16457,7 @@
         </is>
       </c>
       <c r="B1603" t="n">
-        <v>494.3154590733707</v>
+        <v>395.0762272874557</v>
       </c>
     </row>
     <row r="1604">
@@ -16467,7 +16467,7 @@
         </is>
       </c>
       <c r="B1604" t="n">
-        <v>536.6511187231085</v>
+        <v>438.4664744971022</v>
       </c>
     </row>
     <row r="1605">
@@ -16477,7 +16477,7 @@
         </is>
       </c>
       <c r="B1605" t="n">
-        <v>514.4386511470057</v>
+        <v>416.0789905415845</v>
       </c>
     </row>
     <row r="1606">
@@ -16487,7 +16487,7 @@
         </is>
       </c>
       <c r="B1606" t="n">
-        <v>495.4442066712137</v>
+        <v>397.3403193471824</v>
       </c>
     </row>
     <row r="1607">
@@ -16497,7 +16497,7 @@
         </is>
       </c>
       <c r="B1607" t="n">
-        <v>501.9342303686851</v>
+        <v>408.4709174913589</v>
       </c>
     </row>
     <row r="1608">
@@ -16507,7 +16507,7 @@
         </is>
       </c>
       <c r="B1608" t="n">
-        <v>459.9599227483502</v>
+        <v>368.1985803191053</v>
       </c>
     </row>
     <row r="1609">
@@ -16517,7 +16517,7 @@
         </is>
       </c>
       <c r="B1609" t="n">
-        <v>894.4068829565497</v>
+        <v>806.1261502290746</v>
       </c>
     </row>
     <row r="1610">
@@ -16527,7 +16527,7 @@
         </is>
       </c>
       <c r="B1610" t="n">
-        <v>474.5945938517194</v>
+        <v>385.2279222811994</v>
       </c>
     </row>
     <row r="1611">
@@ -16537,7 +16537,7 @@
         </is>
       </c>
       <c r="B1611" t="n">
-        <v>479.7372757005775</v>
+        <v>389.0976188202113</v>
       </c>
     </row>
     <row r="1612">
@@ -16547,7 +16547,7 @@
         </is>
       </c>
       <c r="B1612" t="n">
-        <v>485.218893496473</v>
+        <v>396.8755938853816</v>
       </c>
     </row>
     <row r="1613">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="B1613" t="n">
-        <v>457.2274253920102</v>
+        <v>369.8202292080688</v>
       </c>
     </row>
     <row r="1614">
@@ -16567,7 +16567,7 @@
         </is>
       </c>
       <c r="B1614" t="n">
-        <v>486.9298022703892</v>
+        <v>398.3741967554467</v>
       </c>
     </row>
     <row r="1615">
@@ -16577,7 +16577,7 @@
         </is>
       </c>
       <c r="B1615" t="n">
-        <v>484.7730094320891</v>
+        <v>394.6889631132829</v>
       </c>
     </row>
     <row r="1616">
@@ -16587,7 +16587,7 @@
         </is>
       </c>
       <c r="B1616" t="n">
-        <v>482.2276430235987</v>
+        <v>392.755684146105</v>
       </c>
     </row>
     <row r="1617">
@@ -16597,7 +16597,7 @@
         </is>
       </c>
       <c r="B1617" t="n">
-        <v>488.1188252822096</v>
+        <v>397.5049035715558</v>
       </c>
     </row>
     <row r="1618">
@@ -16607,7 +16607,7 @@
         </is>
       </c>
       <c r="B1618" t="n">
-        <v>495.6579322510516</v>
+        <v>401.7419113913604</v>
       </c>
     </row>
     <row r="1619">
@@ -16617,7 +16617,7 @@
         </is>
       </c>
       <c r="B1619" t="n">
-        <v>524.1518150196667</v>
+        <v>426.1736322238116</v>
       </c>
     </row>
     <row r="1620">
@@ -16627,7 +16627,7 @@
         </is>
       </c>
       <c r="B1620" t="n">
-        <v>570.1177242817644</v>
+        <v>469.9007959816706</v>
       </c>
     </row>
     <row r="1621">
@@ -16637,7 +16637,7 @@
         </is>
       </c>
       <c r="B1621" t="n">
-        <v>571.4318652181396</v>
+        <v>465.9595484207845</v>
       </c>
     </row>
     <row r="1622">
@@ -16647,7 +16647,7 @@
         </is>
       </c>
       <c r="B1622" t="n">
-        <v>529.5740795216229</v>
+        <v>423.3259540530866</v>
       </c>
     </row>
     <row r="1623">
@@ -16657,7 +16657,7 @@
         </is>
       </c>
       <c r="B1623" t="n">
-        <v>511.9114183276154</v>
+        <v>405.6192626145653</v>
       </c>
     </row>
     <row r="1624">
@@ -16667,7 +16667,7 @@
         </is>
       </c>
       <c r="B1624" t="n">
-        <v>547.1298318884034</v>
+        <v>445.7074426012758</v>
       </c>
     </row>
     <row r="1625">
@@ -16677,7 +16677,7 @@
         </is>
       </c>
       <c r="B1625" t="n">
-        <v>531.8617494670865</v>
+        <v>427.3916081855314</v>
       </c>
     </row>
     <row r="1626">
@@ -16687,7 +16687,7 @@
         </is>
       </c>
       <c r="B1626" t="n">
-        <v>493.2742887454199</v>
+        <v>392.5706832419263</v>
       </c>
     </row>
     <row r="1627">
@@ -16697,7 +16697,7 @@
         </is>
       </c>
       <c r="B1627" t="n">
-        <v>494.3154590733707</v>
+        <v>395.0762272874557</v>
       </c>
     </row>
     <row r="1628">
@@ -16707,7 +16707,7 @@
         </is>
       </c>
       <c r="B1628" t="n">
-        <v>536.6511187231085</v>
+        <v>438.4664744971022</v>
       </c>
     </row>
     <row r="1629">
@@ -16717,7 +16717,7 @@
         </is>
       </c>
       <c r="B1629" t="n">
-        <v>514.4386511470057</v>
+        <v>416.0789905415845</v>
       </c>
     </row>
     <row r="1630">
@@ -16727,7 +16727,7 @@
         </is>
       </c>
       <c r="B1630" t="n">
-        <v>495.4442066712137</v>
+        <v>397.3403193471824</v>
       </c>
     </row>
     <row r="1631">
@@ -16737,7 +16737,7 @@
         </is>
       </c>
       <c r="B1631" t="n">
-        <v>501.9342303686851</v>
+        <v>408.4709174913589</v>
       </c>
     </row>
     <row r="1632">
@@ -16747,7 +16747,7 @@
         </is>
       </c>
       <c r="B1632" t="n">
-        <v>459.9599227483502</v>
+        <v>368.1985803191053</v>
       </c>
     </row>
     <row r="1633">
@@ -16757,7 +16757,7 @@
         </is>
       </c>
       <c r="B1633" t="n">
-        <v>894.4068829565497</v>
+        <v>806.1261502290746</v>
       </c>
     </row>
     <row r="1634">
@@ -16767,7 +16767,7 @@
         </is>
       </c>
       <c r="B1634" t="n">
-        <v>474.5945938517194</v>
+        <v>385.2279222811994</v>
       </c>
     </row>
     <row r="1635">
@@ -16777,7 +16777,7 @@
         </is>
       </c>
       <c r="B1635" t="n">
-        <v>479.7372757005775</v>
+        <v>389.0976188202113</v>
       </c>
     </row>
     <row r="1636">
@@ -16787,7 +16787,7 @@
         </is>
       </c>
       <c r="B1636" t="n">
-        <v>485.218893496473</v>
+        <v>396.8755938853816</v>
       </c>
     </row>
     <row r="1637">
@@ -16797,7 +16797,7 @@
         </is>
       </c>
       <c r="B1637" t="n">
-        <v>457.2274253920102</v>
+        <v>369.8202292080688</v>
       </c>
     </row>
     <row r="1638">
@@ -16807,7 +16807,7 @@
         </is>
       </c>
       <c r="B1638" t="n">
-        <v>486.9298022703892</v>
+        <v>398.3741967554467</v>
       </c>
     </row>
     <row r="1639">
@@ -16817,7 +16817,7 @@
         </is>
       </c>
       <c r="B1639" t="n">
-        <v>484.7730094320891</v>
+        <v>394.6889631132829</v>
       </c>
     </row>
     <row r="1640">
@@ -16827,7 +16827,7 @@
         </is>
       </c>
       <c r="B1640" t="n">
-        <v>482.2276430235987</v>
+        <v>392.755684146105</v>
       </c>
     </row>
     <row r="1641">
@@ -16837,7 +16837,7 @@
         </is>
       </c>
       <c r="B1641" t="n">
-        <v>488.1188252822096</v>
+        <v>397.5049035715558</v>
       </c>
     </row>
     <row r="1642">
@@ -16847,7 +16847,7 @@
         </is>
       </c>
       <c r="B1642" t="n">
-        <v>495.6579322510516</v>
+        <v>401.7419113913604</v>
       </c>
     </row>
     <row r="1643">
@@ -16857,7 +16857,7 @@
         </is>
       </c>
       <c r="B1643" t="n">
-        <v>524.1518150196667</v>
+        <v>426.1736322238116</v>
       </c>
     </row>
     <row r="1644">
@@ -16867,7 +16867,7 @@
         </is>
       </c>
       <c r="B1644" t="n">
-        <v>570.1177242817644</v>
+        <v>469.9007959816706</v>
       </c>
     </row>
     <row r="1645">
@@ -16877,7 +16877,7 @@
         </is>
       </c>
       <c r="B1645" t="n">
-        <v>571.4318652181396</v>
+        <v>465.9595484207845</v>
       </c>
     </row>
     <row r="1646">
@@ -16887,7 +16887,7 @@
         </is>
       </c>
       <c r="B1646" t="n">
-        <v>529.5740795216229</v>
+        <v>423.3259540530866</v>
       </c>
     </row>
     <row r="1647">
@@ -16897,7 +16897,7 @@
         </is>
       </c>
       <c r="B1647" t="n">
-        <v>511.9114183276154</v>
+        <v>405.6192626145653</v>
       </c>
     </row>
     <row r="1648">
@@ -16907,7 +16907,7 @@
         </is>
       </c>
       <c r="B1648" t="n">
-        <v>547.1298318884034</v>
+        <v>445.7074426012758</v>
       </c>
     </row>
     <row r="1649">
@@ -16917,7 +16917,7 @@
         </is>
       </c>
       <c r="B1649" t="n">
-        <v>531.8617494670865</v>
+        <v>427.3916081855314</v>
       </c>
     </row>
     <row r="1650">
@@ -16927,7 +16927,7 @@
         </is>
       </c>
       <c r="B1650" t="n">
-        <v>493.2742887454199</v>
+        <v>392.5706832419263</v>
       </c>
     </row>
     <row r="1651">
@@ -16937,7 +16937,7 @@
         </is>
       </c>
       <c r="B1651" t="n">
-        <v>494.3154590733707</v>
+        <v>395.0762272874557</v>
       </c>
     </row>
     <row r="1652">
@@ -16947,7 +16947,7 @@
         </is>
       </c>
       <c r="B1652" t="n">
-        <v>536.6511187231085</v>
+        <v>438.4664744971022</v>
       </c>
     </row>
     <row r="1653">
@@ -16957,7 +16957,7 @@
         </is>
       </c>
       <c r="B1653" t="n">
-        <v>514.4386511470057</v>
+        <v>416.0789905415845</v>
       </c>
     </row>
     <row r="1654">
@@ -16967,7 +16967,7 @@
         </is>
       </c>
       <c r="B1654" t="n">
-        <v>495.4442066712137</v>
+        <v>397.3403193471824</v>
       </c>
     </row>
     <row r="1655">
@@ -16977,7 +16977,7 @@
         </is>
       </c>
       <c r="B1655" t="n">
-        <v>501.9342303686851</v>
+        <v>408.4709174913589</v>
       </c>
     </row>
     <row r="1656">
@@ -16987,7 +16987,7 @@
         </is>
       </c>
       <c r="B1656" t="n">
-        <v>459.9599227483502</v>
+        <v>368.1985803191053</v>
       </c>
     </row>
     <row r="1657">
@@ -16997,7 +16997,7 @@
         </is>
       </c>
       <c r="B1657" t="n">
-        <v>894.4068829565497</v>
+        <v>806.1261502290746</v>
       </c>
     </row>
     <row r="1658">
@@ -17247,7 +17247,7 @@
         </is>
       </c>
       <c r="B1682" t="n">
-        <v>379.6756750813755</v>
+        <v>308.1823378249595</v>
       </c>
     </row>
     <row r="1683">
@@ -17257,7 +17257,7 @@
         </is>
       </c>
       <c r="B1683" t="n">
-        <v>383.789820560462</v>
+        <v>311.278095056169</v>
       </c>
     </row>
     <row r="1684">
@@ -17267,7 +17267,7 @@
         </is>
       </c>
       <c r="B1684" t="n">
-        <v>388.1751147971784</v>
+        <v>317.5004751083053</v>
       </c>
     </row>
     <row r="1685">
@@ -17277,7 +17277,7 @@
         </is>
       </c>
       <c r="B1685" t="n">
-        <v>365.7819403136081</v>
+        <v>295.8561833664551</v>
       </c>
     </row>
     <row r="1686">
@@ -17287,7 +17287,7 @@
         </is>
       </c>
       <c r="B1686" t="n">
-        <v>389.5438418163114</v>
+        <v>318.6993574043574</v>
       </c>
     </row>
     <row r="1687">
@@ -17297,7 +17297,7 @@
         </is>
       </c>
       <c r="B1687" t="n">
-        <v>387.8184075456713</v>
+        <v>315.7511704906263</v>
       </c>
     </row>
     <row r="1688">
@@ -17307,7 +17307,7 @@
         </is>
       </c>
       <c r="B1688" t="n">
-        <v>385.782114418879</v>
+        <v>314.204547316884</v>
       </c>
     </row>
     <row r="1689">
@@ -17317,7 +17317,7 @@
         </is>
       </c>
       <c r="B1689" t="n">
-        <v>390.4950602257676</v>
+        <v>318.0039228572446</v>
       </c>
     </row>
     <row r="1690">
@@ -17327,7 +17327,7 @@
         </is>
       </c>
       <c r="B1690" t="n">
-        <v>396.5263458008413</v>
+        <v>321.3935291130883</v>
       </c>
     </row>
     <row r="1691">
@@ -17337,7 +17337,7 @@
         </is>
       </c>
       <c r="B1691" t="n">
-        <v>419.3214520157334</v>
+        <v>340.9389057790493</v>
       </c>
     </row>
     <row r="1692">
@@ -17347,7 +17347,7 @@
         </is>
       </c>
       <c r="B1692" t="n">
-        <v>456.0941794254115</v>
+        <v>375.9206367853365</v>
       </c>
     </row>
     <row r="1693">
@@ -17357,7 +17357,7 @@
         </is>
       </c>
       <c r="B1693" t="n">
-        <v>457.1454921745117</v>
+        <v>372.7676387366276</v>
       </c>
     </row>
     <row r="1694">
@@ -17367,7 +17367,7 @@
         </is>
       </c>
       <c r="B1694" t="n">
-        <v>423.6592636172983</v>
+        <v>338.6607632424693</v>
       </c>
     </row>
     <row r="1695">
@@ -17377,7 +17377,7 @@
         </is>
       </c>
       <c r="B1695" t="n">
-        <v>409.5291346620923</v>
+        <v>324.4954100916523</v>
       </c>
     </row>
     <row r="1696">
@@ -17387,7 +17387,7 @@
         </is>
       </c>
       <c r="B1696" t="n">
-        <v>437.7038655107227</v>
+        <v>356.5659540810207</v>
       </c>
     </row>
     <row r="1697">
@@ -17397,7 +17397,7 @@
         </is>
       </c>
       <c r="B1697" t="n">
-        <v>425.4893995736692</v>
+        <v>341.9132865484251</v>
       </c>
     </row>
     <row r="1698">
@@ -17407,7 +17407,7 @@
         </is>
       </c>
       <c r="B1698" t="n">
-        <v>394.619430996336</v>
+        <v>314.056546593541</v>
       </c>
     </row>
     <row r="1699">
@@ -17417,7 +17417,7 @@
         </is>
       </c>
       <c r="B1699" t="n">
-        <v>395.4523672586966</v>
+        <v>316.0609818299645</v>
       </c>
     </row>
     <row r="1700">
@@ -17427,7 +17427,7 @@
         </is>
       </c>
       <c r="B1700" t="n">
-        <v>429.3208949784868</v>
+        <v>350.7731795976818</v>
       </c>
     </row>
     <row r="1701">
@@ -17437,7 +17437,7 @@
         </is>
       </c>
       <c r="B1701" t="n">
-        <v>411.5509209176046</v>
+        <v>332.8631924332676</v>
       </c>
     </row>
     <row r="1702">
@@ -17447,7 +17447,7 @@
         </is>
       </c>
       <c r="B1702" t="n">
-        <v>396.355365336971</v>
+        <v>317.8722554777459</v>
       </c>
     </row>
     <row r="1703">
@@ -17457,7 +17457,7 @@
         </is>
       </c>
       <c r="B1703" t="n">
-        <v>401.5473842949481</v>
+        <v>326.7767339930871</v>
       </c>
     </row>
     <row r="1704">
@@ -17467,7 +17467,7 @@
         </is>
       </c>
       <c r="B1704" t="n">
-        <v>367.9679381986801</v>
+        <v>294.5588642552842</v>
       </c>
     </row>
     <row r="1705">
@@ -17477,7 +17477,7 @@
         </is>
       </c>
       <c r="B1705" t="n">
-        <v>715.5255063652397</v>
+        <v>644.9009201832597</v>
       </c>
     </row>
     <row r="1706">
@@ -18327,7 +18327,7 @@
         </is>
       </c>
       <c r="B1790" t="n">
-        <v>42.42304310220572</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1791">
@@ -18337,7 +18337,7 @@
         </is>
       </c>
       <c r="B1791" t="n">
-        <v>9.114386773609297</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1792">
@@ -18357,7 +18357,7 @@
         </is>
       </c>
       <c r="B1793" t="n">
-        <v>55.41304873842141</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1794">
@@ -18367,7 +18367,7 @@
         </is>
       </c>
       <c r="B1794" t="n">
-        <v>25.23605282375498</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1795">
@@ -18427,7 +18427,7 @@
         </is>
       </c>
       <c r="B1800" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="1801">
@@ -18667,7 +18667,7 @@
         </is>
       </c>
       <c r="B1824" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1825">
@@ -18807,7 +18807,7 @@
         </is>
       </c>
       <c r="B1838" t="n">
-        <v>169.3418492433048</v>
+        <v>237.218718206834</v>
       </c>
     </row>
     <row r="1839">
@@ -18817,7 +18817,7 @@
         </is>
       </c>
       <c r="B1839" t="n">
-        <v>144.4221588528595</v>
+        <v>159.0051776906344</v>
       </c>
     </row>
     <row r="1840">
@@ -18837,7 +18837,7 @@
         </is>
       </c>
       <c r="B1841" t="n">
-        <v>112.6463564427249</v>
+        <v>201.3072344241991</v>
       </c>
     </row>
     <row r="1842">
@@ -18847,7 +18847,7 @@
         </is>
       </c>
       <c r="B1842" t="n">
-        <v>106.6740939846233</v>
+        <v>147.0517785026312</v>
       </c>
     </row>
     <row r="1843">
@@ -19127,7 +19127,7 @@
         </is>
       </c>
       <c r="B1870" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1871">
@@ -19147,7 +19147,7 @@
         </is>
       </c>
       <c r="B1872" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1873">
@@ -19647,7 +19647,7 @@
         </is>
       </c>
       <c r="B1922" t="n">
-        <v>379.6756750813755</v>
+        <v>308.1823378249595</v>
       </c>
     </row>
     <row r="1923">
@@ -19657,7 +19657,7 @@
         </is>
       </c>
       <c r="B1923" t="n">
-        <v>383.789820560462</v>
+        <v>311.278095056169</v>
       </c>
     </row>
     <row r="1924">
@@ -19667,7 +19667,7 @@
         </is>
       </c>
       <c r="B1924" t="n">
-        <v>388.1751147971784</v>
+        <v>317.5004751083053</v>
       </c>
     </row>
     <row r="1925">
@@ -19677,7 +19677,7 @@
         </is>
       </c>
       <c r="B1925" t="n">
-        <v>365.7819403136081</v>
+        <v>295.8561833664551</v>
       </c>
     </row>
     <row r="1926">
@@ -19687,7 +19687,7 @@
         </is>
       </c>
       <c r="B1926" t="n">
-        <v>389.5438418163114</v>
+        <v>318.6993574043574</v>
       </c>
     </row>
     <row r="1927">
@@ -19697,7 +19697,7 @@
         </is>
       </c>
       <c r="B1927" t="n">
-        <v>387.8184075456713</v>
+        <v>315.7511704906263</v>
       </c>
     </row>
     <row r="1928">
@@ -19707,7 +19707,7 @@
         </is>
       </c>
       <c r="B1928" t="n">
-        <v>385.782114418879</v>
+        <v>314.204547316884</v>
       </c>
     </row>
     <row r="1929">
@@ -19717,7 +19717,7 @@
         </is>
       </c>
       <c r="B1929" t="n">
-        <v>390.4950602257676</v>
+        <v>318.0039228572446</v>
       </c>
     </row>
     <row r="1930">
@@ -19727,7 +19727,7 @@
         </is>
       </c>
       <c r="B1930" t="n">
-        <v>396.5263458008413</v>
+        <v>321.3935291130883</v>
       </c>
     </row>
     <row r="1931">
@@ -19737,7 +19737,7 @@
         </is>
       </c>
       <c r="B1931" t="n">
-        <v>419.3214520157334</v>
+        <v>340.9389057790493</v>
       </c>
     </row>
     <row r="1932">
@@ -19747,7 +19747,7 @@
         </is>
       </c>
       <c r="B1932" t="n">
-        <v>456.0941794254115</v>
+        <v>375.9206367853365</v>
       </c>
     </row>
     <row r="1933">
@@ -19757,7 +19757,7 @@
         </is>
       </c>
       <c r="B1933" t="n">
-        <v>457.1454921745117</v>
+        <v>372.7676387366276</v>
       </c>
     </row>
     <row r="1934">
@@ -19767,7 +19767,7 @@
         </is>
       </c>
       <c r="B1934" t="n">
-        <v>423.6592636172983</v>
+        <v>338.6607632424693</v>
       </c>
     </row>
     <row r="1935">
@@ -19777,7 +19777,7 @@
         </is>
       </c>
       <c r="B1935" t="n">
-        <v>409.5291346620923</v>
+        <v>324.4954100916523</v>
       </c>
     </row>
     <row r="1936">
@@ -19787,7 +19787,7 @@
         </is>
       </c>
       <c r="B1936" t="n">
-        <v>437.7038655107227</v>
+        <v>356.5659540810207</v>
       </c>
     </row>
     <row r="1937">
@@ -19797,7 +19797,7 @@
         </is>
       </c>
       <c r="B1937" t="n">
-        <v>425.4893995736692</v>
+        <v>341.9132865484251</v>
       </c>
     </row>
     <row r="1938">
@@ -19807,7 +19807,7 @@
         </is>
       </c>
       <c r="B1938" t="n">
-        <v>394.619430996336</v>
+        <v>314.056546593541</v>
       </c>
     </row>
     <row r="1939">
@@ -19817,7 +19817,7 @@
         </is>
       </c>
       <c r="B1939" t="n">
-        <v>395.4523672586966</v>
+        <v>316.0609818299645</v>
       </c>
     </row>
     <row r="1940">
@@ -19827,7 +19827,7 @@
         </is>
       </c>
       <c r="B1940" t="n">
-        <v>429.3208949784868</v>
+        <v>350.7731795976818</v>
       </c>
     </row>
     <row r="1941">
@@ -19837,7 +19837,7 @@
         </is>
       </c>
       <c r="B1941" t="n">
-        <v>411.5509209176046</v>
+        <v>332.8631924332676</v>
       </c>
     </row>
     <row r="1942">
@@ -19847,7 +19847,7 @@
         </is>
       </c>
       <c r="B1942" t="n">
-        <v>396.355365336971</v>
+        <v>317.8722554777459</v>
       </c>
     </row>
     <row r="1943">
@@ -19857,7 +19857,7 @@
         </is>
       </c>
       <c r="B1943" t="n">
-        <v>401.5473842949481</v>
+        <v>326.7767339930871</v>
       </c>
     </row>
     <row r="1944">
@@ -19867,7 +19867,7 @@
         </is>
       </c>
       <c r="B1944" t="n">
-        <v>367.9679381986801</v>
+        <v>294.5588642552842</v>
       </c>
     </row>
     <row r="1945">
@@ -19877,7 +19877,7 @@
         </is>
       </c>
       <c r="B1945" t="n">
-        <v>715.5255063652397</v>
+        <v>644.9009201832597</v>
       </c>
     </row>
     <row r="1946">
@@ -19887,7 +19887,7 @@
         </is>
       </c>
       <c r="B1946" t="n">
-        <v>379.6756750813755</v>
+        <v>308.1823378249595</v>
       </c>
     </row>
     <row r="1947">
@@ -19897,7 +19897,7 @@
         </is>
       </c>
       <c r="B1947" t="n">
-        <v>383.789820560462</v>
+        <v>311.278095056169</v>
       </c>
     </row>
     <row r="1948">
@@ -19907,7 +19907,7 @@
         </is>
       </c>
       <c r="B1948" t="n">
-        <v>388.1751147971784</v>
+        <v>317.5004751083053</v>
       </c>
     </row>
     <row r="1949">
@@ -19917,7 +19917,7 @@
         </is>
       </c>
       <c r="B1949" t="n">
-        <v>365.7819403136081</v>
+        <v>295.8561833664551</v>
       </c>
     </row>
     <row r="1950">
@@ -19927,7 +19927,7 @@
         </is>
       </c>
       <c r="B1950" t="n">
-        <v>389.5438418163114</v>
+        <v>318.6993574043574</v>
       </c>
     </row>
     <row r="1951">
@@ -19937,7 +19937,7 @@
         </is>
       </c>
       <c r="B1951" t="n">
-        <v>387.8184075456713</v>
+        <v>315.7511704906263</v>
       </c>
     </row>
     <row r="1952">
@@ -19947,7 +19947,7 @@
         </is>
       </c>
       <c r="B1952" t="n">
-        <v>385.782114418879</v>
+        <v>314.204547316884</v>
       </c>
     </row>
     <row r="1953">
@@ -19957,7 +19957,7 @@
         </is>
       </c>
       <c r="B1953" t="n">
-        <v>390.4950602257676</v>
+        <v>318.0039228572446</v>
       </c>
     </row>
     <row r="1954">
@@ -19967,7 +19967,7 @@
         </is>
       </c>
       <c r="B1954" t="n">
-        <v>396.5263458008413</v>
+        <v>321.3935291130883</v>
       </c>
     </row>
     <row r="1955">
@@ -19977,7 +19977,7 @@
         </is>
       </c>
       <c r="B1955" t="n">
-        <v>419.3214520157334</v>
+        <v>340.9389057790493</v>
       </c>
     </row>
     <row r="1956">
@@ -19987,7 +19987,7 @@
         </is>
       </c>
       <c r="B1956" t="n">
-        <v>456.0941794254115</v>
+        <v>375.9206367853365</v>
       </c>
     </row>
     <row r="1957">
@@ -19997,7 +19997,7 @@
         </is>
       </c>
       <c r="B1957" t="n">
-        <v>457.1454921745117</v>
+        <v>372.7676387366276</v>
       </c>
     </row>
     <row r="1958">
@@ -20007,7 +20007,7 @@
         </is>
       </c>
       <c r="B1958" t="n">
-        <v>423.6592636172983</v>
+        <v>338.6607632424693</v>
       </c>
     </row>
     <row r="1959">
@@ -20017,7 +20017,7 @@
         </is>
       </c>
       <c r="B1959" t="n">
-        <v>409.5291346620923</v>
+        <v>324.4954100916523</v>
       </c>
     </row>
     <row r="1960">
@@ -20027,7 +20027,7 @@
         </is>
       </c>
       <c r="B1960" t="n">
-        <v>437.7038655107227</v>
+        <v>356.5659540810207</v>
       </c>
     </row>
     <row r="1961">
@@ -20037,7 +20037,7 @@
         </is>
       </c>
       <c r="B1961" t="n">
-        <v>425.4893995736692</v>
+        <v>341.9132865484251</v>
       </c>
     </row>
     <row r="1962">
@@ -20047,7 +20047,7 @@
         </is>
       </c>
       <c r="B1962" t="n">
-        <v>394.619430996336</v>
+        <v>314.056546593541</v>
       </c>
     </row>
     <row r="1963">
@@ -20057,7 +20057,7 @@
         </is>
       </c>
       <c r="B1963" t="n">
-        <v>395.4523672586966</v>
+        <v>316.0609818299645</v>
       </c>
     </row>
     <row r="1964">
@@ -20067,7 +20067,7 @@
         </is>
       </c>
       <c r="B1964" t="n">
-        <v>429.3208949784868</v>
+        <v>350.7731795976818</v>
       </c>
     </row>
     <row r="1965">
@@ -20077,7 +20077,7 @@
         </is>
       </c>
       <c r="B1965" t="n">
-        <v>411.5509209176046</v>
+        <v>332.8631924332676</v>
       </c>
     </row>
     <row r="1966">
@@ -20087,7 +20087,7 @@
         </is>
       </c>
       <c r="B1966" t="n">
-        <v>396.355365336971</v>
+        <v>317.8722554777459</v>
       </c>
     </row>
     <row r="1967">
@@ -20097,7 +20097,7 @@
         </is>
       </c>
       <c r="B1967" t="n">
-        <v>401.5473842949481</v>
+        <v>326.7767339930871</v>
       </c>
     </row>
     <row r="1968">
@@ -20107,7 +20107,7 @@
         </is>
       </c>
       <c r="B1968" t="n">
-        <v>367.9679381986801</v>
+        <v>294.5588642552842</v>
       </c>
     </row>
     <row r="1969">
@@ -20117,7 +20117,7 @@
         </is>
       </c>
       <c r="B1969" t="n">
-        <v>715.5255063652397</v>
+        <v>644.9009201832597</v>
       </c>
     </row>
     <row r="1970">
@@ -20127,7 +20127,7 @@
         </is>
       </c>
       <c r="B1970" t="n">
-        <v>52.95802759734534</v>
+        <v>68.84543587654889</v>
       </c>
     </row>
     <row r="1971">
@@ -20137,7 +20137,7 @@
         </is>
       </c>
       <c r="B1971" t="n">
-        <v>53.71238926243911</v>
+        <v>69.82610604117089</v>
       </c>
     </row>
     <row r="1972">
@@ -20147,7 +20147,7 @@
         </is>
       </c>
       <c r="B1972" t="n">
-        <v>52.35158495472066</v>
+        <v>68.0570604411369</v>
       </c>
     </row>
     <row r="1973">
@@ -20157,7 +20157,7 @@
         </is>
       </c>
       <c r="B1973" t="n">
-        <v>51.79685699789111</v>
+        <v>67.33591409725845</v>
       </c>
     </row>
     <row r="1974">
@@ -20167,7 +20167,7 @@
         </is>
       </c>
       <c r="B1974" t="n">
-        <v>52.47739586070644</v>
+        <v>68.22061461891843</v>
       </c>
     </row>
     <row r="1975">
@@ -20177,7 +20177,7 @@
         </is>
       </c>
       <c r="B1975" t="n">
-        <v>53.38313855929245</v>
+        <v>69.39808012708022</v>
       </c>
     </row>
     <row r="1976">
@@ -20187,7 +20187,7 @@
         </is>
       </c>
       <c r="B1976" t="n">
-        <v>53.02042007555156</v>
+        <v>68.9265460982171</v>
       </c>
     </row>
     <row r="1977">
@@ -20197,7 +20197,7 @@
         </is>
       </c>
       <c r="B1977" t="n">
-        <v>53.69713879149867</v>
+        <v>69.80628042894823</v>
       </c>
     </row>
     <row r="1978">
@@ -20207,7 +20207,7 @@
         </is>
       </c>
       <c r="B1978" t="n">
-        <v>55.65393828722467</v>
+        <v>72.35011977339201</v>
       </c>
     </row>
     <row r="1979">
@@ -20217,7 +20217,7 @@
         </is>
       </c>
       <c r="B1979" t="n">
-        <v>58.06114536050666</v>
+        <v>75.47948896865867</v>
       </c>
     </row>
     <row r="1980">
@@ -20227,7 +20227,7 @@
         </is>
       </c>
       <c r="B1980" t="n">
-        <v>59.38780936301888</v>
+        <v>77.20415217192445</v>
       </c>
     </row>
     <row r="1981">
@@ -20237,7 +20237,7 @@
         </is>
       </c>
       <c r="B1981" t="n">
-        <v>62.50211365769155</v>
+        <v>81.25274775499912</v>
       </c>
     </row>
     <row r="1982">
@@ -20247,7 +20247,7 @@
         </is>
       </c>
       <c r="B1982" t="n">
-        <v>62.96185212950267</v>
+        <v>81.85040776835356</v>
       </c>
     </row>
     <row r="1983">
@@ -20257,7 +20257,7 @@
         </is>
       </c>
       <c r="B1983" t="n">
-        <v>62.98794412625199</v>
+        <v>81.88432736412756</v>
       </c>
     </row>
     <row r="1984">
@@ -20267,7 +20267,7 @@
         </is>
       </c>
       <c r="B1984" t="n">
-        <v>60.10215661459443</v>
+        <v>78.13280359897266</v>
       </c>
     </row>
     <row r="1985">
@@ -20277,7 +20277,7 @@
         </is>
       </c>
       <c r="B1985" t="n">
-        <v>61.90823187055111</v>
+        <v>80.48070143171645</v>
       </c>
     </row>
     <row r="1986">
@@ -20287,7 +20287,7 @@
         </is>
       </c>
       <c r="B1986" t="n">
-        <v>59.67621066873668</v>
+        <v>77.57907386935777</v>
       </c>
     </row>
     <row r="1987">
@@ -20297,7 +20297,7 @@
         </is>
       </c>
       <c r="B1987" t="n">
-        <v>58.80843365091266</v>
+        <v>76.45096374618645</v>
       </c>
     </row>
     <row r="1988">
@@ -20307,7 +20307,7 @@
         </is>
       </c>
       <c r="B1988" t="n">
-        <v>58.18349287466999</v>
+        <v>75.63854073707111</v>
       </c>
     </row>
     <row r="1989">
@@ -20317,7 +20317,7 @@
         </is>
       </c>
       <c r="B1989" t="n">
-        <v>58.28720628469379</v>
+        <v>75.773368170102</v>
       </c>
     </row>
     <row r="1990">
@@ -20327,7 +20327,7 @@
         </is>
       </c>
       <c r="B1990" t="n">
-        <v>58.13563693275955</v>
+        <v>75.57632801258734</v>
       </c>
     </row>
     <row r="1991">
@@ -20337,7 +20337,7 @@
         </is>
       </c>
       <c r="B1991" t="n">
-        <v>55.38566689026712</v>
+        <v>72.00136695734733</v>
       </c>
     </row>
     <row r="1992">
@@ -20347,7 +20347,7 @@
         </is>
       </c>
       <c r="B1992" t="n">
-        <v>54.37709180992267</v>
+        <v>70.69021935289955</v>
       </c>
     </row>
     <row r="1993">
@@ -20357,7 +20357,7 @@
         </is>
       </c>
       <c r="B1993" t="n">
-        <v>52.31450828294845</v>
+        <v>68.0088607678329</v>
       </c>
     </row>
     <row r="1994">
@@ -20367,7 +20367,7 @@
         </is>
       </c>
       <c r="B1994" t="n">
-        <v>238.311124188054</v>
+        <v>309.80446144447</v>
       </c>
     </row>
     <row r="1995">
@@ -20377,7 +20377,7 @@
         </is>
       </c>
       <c r="B1995" t="n">
-        <v>241.705751680976</v>
+        <v>314.217477185269</v>
       </c>
     </row>
     <row r="1996">
@@ -20387,7 +20387,7 @@
         </is>
       </c>
       <c r="B1996" t="n">
-        <v>235.582132296243</v>
+        <v>306.2567719851161</v>
       </c>
     </row>
     <row r="1997">
@@ -20397,7 +20397,7 @@
         </is>
       </c>
       <c r="B1997" t="n">
-        <v>233.08585649051</v>
+        <v>303.0116134376631</v>
       </c>
     </row>
     <row r="1998">
@@ -20407,7 +20407,7 @@
         </is>
       </c>
       <c r="B1998" t="n">
-        <v>236.148281373179</v>
+        <v>306.992765785133</v>
       </c>
     </row>
     <row r="1999">
@@ -20417,7 +20417,7 @@
         </is>
       </c>
       <c r="B1999" t="n">
-        <v>240.224123516816</v>
+        <v>312.291360571861</v>
       </c>
     </row>
     <row r="2000">
@@ -20427,7 +20427,7 @@
         </is>
       </c>
       <c r="B2000" t="n">
-        <v>238.591890339982</v>
+        <v>310.169457441977</v>
       </c>
     </row>
     <row r="2001">
@@ -20437,7 +20437,7 @@
         </is>
       </c>
       <c r="B2001" t="n">
-        <v>241.637124561744</v>
+        <v>314.1282619302671</v>
       </c>
     </row>
     <row r="2002">
@@ -20447,7 +20447,7 @@
         </is>
       </c>
       <c r="B2002" t="n">
-        <v>250.442722292511</v>
+        <v>325.5755389802641</v>
       </c>
     </row>
     <row r="2003">
@@ -20457,7 +20457,7 @@
         </is>
       </c>
       <c r="B2003" t="n">
-        <v>261.27515412228</v>
+        <v>339.6577003589641</v>
       </c>
     </row>
     <row r="2004">
@@ -20467,7 +20467,7 @@
         </is>
       </c>
       <c r="B2004" t="n">
-        <v>267.245142133585</v>
+        <v>347.4186847736601</v>
       </c>
     </row>
     <row r="2005">
@@ -20477,7 +20477,7 @@
         </is>
       </c>
       <c r="B2005" t="n">
-        <v>281.259511459612</v>
+        <v>365.6373648974961</v>
       </c>
     </row>
     <row r="2006">
@@ -20487,7 +20487,7 @@
         </is>
       </c>
       <c r="B2006" t="n">
-        <v>283.328334582762</v>
+        <v>368.3268349575911</v>
       </c>
     </row>
     <row r="2007">
@@ -20497,7 +20497,7 @@
         </is>
       </c>
       <c r="B2007" t="n">
-        <v>283.445748568134</v>
+        <v>368.479473138574</v>
       </c>
     </row>
     <row r="2008">
@@ -20507,7 +20507,7 @@
         </is>
       </c>
       <c r="B2008" t="n">
-        <v>270.459704765675</v>
+        <v>351.597616195377</v>
       </c>
     </row>
     <row r="2009">
@@ -20517,7 +20517,7 @@
         </is>
       </c>
       <c r="B2009" t="n">
-        <v>278.58704341748</v>
+        <v>362.1631564427241</v>
       </c>
     </row>
     <row r="2010">
@@ -20527,7 +20527,7 @@
         </is>
       </c>
       <c r="B2010" t="n">
-        <v>268.5429480093151</v>
+        <v>349.10583241211</v>
       </c>
     </row>
     <row r="2011">
@@ -20537,7 +20537,7 @@
         </is>
       </c>
       <c r="B2011" t="n">
-        <v>264.637951429107</v>
+        <v>344.029336857839</v>
       </c>
     </row>
     <row r="2012">
@@ -20547,7 +20547,7 @@
         </is>
       </c>
       <c r="B2012" t="n">
-        <v>261.825717936015</v>
+        <v>340.37343331682</v>
       </c>
     </row>
     <row r="2013">
@@ -20557,7 +20557,7 @@
         </is>
       </c>
       <c r="B2013" t="n">
-        <v>262.2924282811221</v>
+        <v>340.980156765459</v>
       </c>
     </row>
     <row r="2014">
@@ -20567,7 +20567,7 @@
         </is>
       </c>
       <c r="B2014" t="n">
-        <v>261.610366197418</v>
+        <v>340.0934760566431</v>
       </c>
     </row>
     <row r="2015">
@@ -20577,7 +20577,7 @@
         </is>
       </c>
       <c r="B2015" t="n">
-        <v>249.235501006202</v>
+        <v>324.006151308063</v>
       </c>
     </row>
     <row r="2016">
@@ -20587,7 +20587,7 @@
         </is>
       </c>
       <c r="B2016" t="n">
-        <v>244.696913144652</v>
+        <v>318.105987088048</v>
       </c>
     </row>
     <row r="2017">
@@ -20597,7 +20597,7 @@
         </is>
       </c>
       <c r="B2017" t="n">
-        <v>235.415287273268</v>
+        <v>306.0398734552481</v>
       </c>
     </row>
     <row r="2018">
@@ -20607,7 +20607,7 @@
         </is>
       </c>
       <c r="B2018" t="n">
-        <v>238.311124188054</v>
+        <v>309.80446144447</v>
       </c>
     </row>
     <row r="2019">
@@ -20617,7 +20617,7 @@
         </is>
       </c>
       <c r="B2019" t="n">
-        <v>241.705751680976</v>
+        <v>314.217477185269</v>
       </c>
     </row>
     <row r="2020">
@@ -20627,7 +20627,7 @@
         </is>
       </c>
       <c r="B2020" t="n">
-        <v>235.582132296243</v>
+        <v>306.2567719851161</v>
       </c>
     </row>
     <row r="2021">
@@ -20637,7 +20637,7 @@
         </is>
       </c>
       <c r="B2021" t="n">
-        <v>233.08585649051</v>
+        <v>303.0116134376631</v>
       </c>
     </row>
     <row r="2022">
@@ -20647,7 +20647,7 @@
         </is>
       </c>
       <c r="B2022" t="n">
-        <v>236.148281373179</v>
+        <v>306.992765785133</v>
       </c>
     </row>
     <row r="2023">
@@ -20657,7 +20657,7 @@
         </is>
       </c>
       <c r="B2023" t="n">
-        <v>240.224123516816</v>
+        <v>312.291360571861</v>
       </c>
     </row>
     <row r="2024">
@@ -20667,7 +20667,7 @@
         </is>
       </c>
       <c r="B2024" t="n">
-        <v>238.591890339982</v>
+        <v>310.169457441977</v>
       </c>
     </row>
     <row r="2025">
@@ -20677,7 +20677,7 @@
         </is>
       </c>
       <c r="B2025" t="n">
-        <v>241.637124561744</v>
+        <v>314.1282619302671</v>
       </c>
     </row>
     <row r="2026">
@@ -20687,7 +20687,7 @@
         </is>
       </c>
       <c r="B2026" t="n">
-        <v>250.442722292511</v>
+        <v>325.5755389802641</v>
       </c>
     </row>
     <row r="2027">
@@ -20697,7 +20697,7 @@
         </is>
       </c>
       <c r="B2027" t="n">
-        <v>261.27515412228</v>
+        <v>339.6577003589641</v>
       </c>
     </row>
     <row r="2028">
@@ -20707,7 +20707,7 @@
         </is>
       </c>
       <c r="B2028" t="n">
-        <v>267.245142133585</v>
+        <v>347.4186847736601</v>
       </c>
     </row>
     <row r="2029">
@@ -20717,7 +20717,7 @@
         </is>
       </c>
       <c r="B2029" t="n">
-        <v>281.259511459612</v>
+        <v>365.6373648974961</v>
       </c>
     </row>
     <row r="2030">
@@ -20727,7 +20727,7 @@
         </is>
       </c>
       <c r="B2030" t="n">
-        <v>283.328334582762</v>
+        <v>368.3268349575911</v>
       </c>
     </row>
     <row r="2031">
@@ -20737,7 +20737,7 @@
         </is>
       </c>
       <c r="B2031" t="n">
-        <v>283.445748568134</v>
+        <v>368.479473138574</v>
       </c>
     </row>
     <row r="2032">
@@ -20747,7 +20747,7 @@
         </is>
       </c>
       <c r="B2032" t="n">
-        <v>270.459704765675</v>
+        <v>351.597616195377</v>
       </c>
     </row>
     <row r="2033">
@@ -20757,7 +20757,7 @@
         </is>
       </c>
       <c r="B2033" t="n">
-        <v>278.58704341748</v>
+        <v>362.1631564427241</v>
       </c>
     </row>
     <row r="2034">
@@ -20767,7 +20767,7 @@
         </is>
       </c>
       <c r="B2034" t="n">
-        <v>268.5429480093151</v>
+        <v>349.10583241211</v>
       </c>
     </row>
     <row r="2035">
@@ -20777,7 +20777,7 @@
         </is>
       </c>
       <c r="B2035" t="n">
-        <v>264.637951429107</v>
+        <v>344.029336857839</v>
       </c>
     </row>
     <row r="2036">
@@ -20787,7 +20787,7 @@
         </is>
       </c>
       <c r="B2036" t="n">
-        <v>261.825717936015</v>
+        <v>340.37343331682</v>
       </c>
     </row>
     <row r="2037">
@@ -20797,7 +20797,7 @@
         </is>
       </c>
       <c r="B2037" t="n">
-        <v>262.2924282811221</v>
+        <v>340.980156765459</v>
       </c>
     </row>
     <row r="2038">
@@ -20807,7 +20807,7 @@
         </is>
       </c>
       <c r="B2038" t="n">
-        <v>261.610366197418</v>
+        <v>340.0934760566431</v>
       </c>
     </row>
     <row r="2039">
@@ -20817,7 +20817,7 @@
         </is>
       </c>
       <c r="B2039" t="n">
-        <v>249.235501006202</v>
+        <v>324.006151308063</v>
       </c>
     </row>
     <row r="2040">
@@ -20827,7 +20827,7 @@
         </is>
       </c>
       <c r="B2040" t="n">
-        <v>244.696913144652</v>
+        <v>318.105987088048</v>
       </c>
     </row>
     <row r="2041">
@@ -20837,7 +20837,7 @@
         </is>
       </c>
       <c r="B2041" t="n">
-        <v>235.415287273268</v>
+        <v>306.0398734552481</v>
       </c>
     </row>
     <row r="2042">
@@ -20847,7 +20847,7 @@
         </is>
       </c>
       <c r="B2042" t="n">
-        <v>238.311124188054</v>
+        <v>309.80446144447</v>
       </c>
     </row>
     <row r="2043">
@@ -20857,7 +20857,7 @@
         </is>
       </c>
       <c r="B2043" t="n">
-        <v>241.705751680976</v>
+        <v>314.217477185269</v>
       </c>
     </row>
     <row r="2044">
@@ -20867,7 +20867,7 @@
         </is>
       </c>
       <c r="B2044" t="n">
-        <v>235.582132296243</v>
+        <v>306.2567719851161</v>
       </c>
     </row>
     <row r="2045">
@@ -20877,7 +20877,7 @@
         </is>
       </c>
       <c r="B2045" t="n">
-        <v>233.08585649051</v>
+        <v>303.0116134376631</v>
       </c>
     </row>
     <row r="2046">
@@ -20887,7 +20887,7 @@
         </is>
       </c>
       <c r="B2046" t="n">
-        <v>236.148281373179</v>
+        <v>306.992765785133</v>
       </c>
     </row>
     <row r="2047">
@@ -20897,7 +20897,7 @@
         </is>
       </c>
       <c r="B2047" t="n">
-        <v>240.224123516816</v>
+        <v>312.291360571861</v>
       </c>
     </row>
     <row r="2048">
@@ -20907,7 +20907,7 @@
         </is>
       </c>
       <c r="B2048" t="n">
-        <v>238.591890339982</v>
+        <v>310.169457441977</v>
       </c>
     </row>
     <row r="2049">
@@ -20917,7 +20917,7 @@
         </is>
       </c>
       <c r="B2049" t="n">
-        <v>241.637124561744</v>
+        <v>314.1282619302671</v>
       </c>
     </row>
     <row r="2050">
@@ -20927,7 +20927,7 @@
         </is>
       </c>
       <c r="B2050" t="n">
-        <v>250.442722292511</v>
+        <v>325.5755389802641</v>
       </c>
     </row>
     <row r="2051">
@@ -20937,7 +20937,7 @@
         </is>
       </c>
       <c r="B2051" t="n">
-        <v>261.27515412228</v>
+        <v>339.6577003589641</v>
       </c>
     </row>
     <row r="2052">
@@ -20947,7 +20947,7 @@
         </is>
       </c>
       <c r="B2052" t="n">
-        <v>267.245142133585</v>
+        <v>347.4186847736601</v>
       </c>
     </row>
     <row r="2053">
@@ -20957,7 +20957,7 @@
         </is>
       </c>
       <c r="B2053" t="n">
-        <v>281.259511459612</v>
+        <v>365.6373648974961</v>
       </c>
     </row>
     <row r="2054">
@@ -20967,7 +20967,7 @@
         </is>
       </c>
       <c r="B2054" t="n">
-        <v>283.328334582762</v>
+        <v>368.3268349575911</v>
       </c>
     </row>
     <row r="2055">
@@ -20977,7 +20977,7 @@
         </is>
       </c>
       <c r="B2055" t="n">
-        <v>283.445748568134</v>
+        <v>368.479473138574</v>
       </c>
     </row>
     <row r="2056">
@@ -20987,7 +20987,7 @@
         </is>
       </c>
       <c r="B2056" t="n">
-        <v>270.459704765675</v>
+        <v>351.597616195377</v>
       </c>
     </row>
     <row r="2057">
@@ -20997,7 +20997,7 @@
         </is>
       </c>
       <c r="B2057" t="n">
-        <v>278.58704341748</v>
+        <v>362.1631564427241</v>
       </c>
     </row>
     <row r="2058">
@@ -21007,7 +21007,7 @@
         </is>
       </c>
       <c r="B2058" t="n">
-        <v>268.5429480093151</v>
+        <v>349.10583241211</v>
       </c>
     </row>
     <row r="2059">
@@ -21017,7 +21017,7 @@
         </is>
       </c>
       <c r="B2059" t="n">
-        <v>264.637951429107</v>
+        <v>344.029336857839</v>
       </c>
     </row>
     <row r="2060">
@@ -21027,7 +21027,7 @@
         </is>
       </c>
       <c r="B2060" t="n">
-        <v>261.825717936015</v>
+        <v>340.37343331682</v>
       </c>
     </row>
     <row r="2061">
@@ -21037,7 +21037,7 @@
         </is>
       </c>
       <c r="B2061" t="n">
-        <v>262.2924282811221</v>
+        <v>340.980156765459</v>
       </c>
     </row>
     <row r="2062">
@@ -21047,7 +21047,7 @@
         </is>
       </c>
       <c r="B2062" t="n">
-        <v>261.610366197418</v>
+        <v>340.0934760566431</v>
       </c>
     </row>
     <row r="2063">
@@ -21057,7 +21057,7 @@
         </is>
       </c>
       <c r="B2063" t="n">
-        <v>249.235501006202</v>
+        <v>324.006151308063</v>
       </c>
     </row>
     <row r="2064">
@@ -21067,7 +21067,7 @@
         </is>
       </c>
       <c r="B2064" t="n">
-        <v>244.696913144652</v>
+        <v>318.105987088048</v>
       </c>
     </row>
     <row r="2065">
@@ -21077,7 +21077,7 @@
         </is>
       </c>
       <c r="B2065" t="n">
-        <v>235.415287273268</v>
+        <v>306.0398734552481</v>
       </c>
     </row>
     <row r="2066">
@@ -21087,7 +21087,7 @@
         </is>
       </c>
       <c r="B2066" t="n">
-        <v>516.7949783632133</v>
+        <v>1036.446623393087</v>
       </c>
     </row>
     <row r="2067">
@@ -21097,7 +21097,7 @@
         </is>
       </c>
       <c r="B2067" t="n">
-        <v>376.2130939979259</v>
+        <v>846.1228546625215</v>
       </c>
     </row>
     <row r="2068">
@@ -21107,7 +21107,7 @@
         </is>
       </c>
       <c r="B2068" t="n">
-        <v>506.876813267751</v>
+        <v>1017.683626535502</v>
       </c>
     </row>
     <row r="2069">
@@ -21117,7 +21117,7 @@
         </is>
       </c>
       <c r="B2069" t="n">
-        <v>512.9451417905049</v>
+        <v>991.4602835810099</v>
       </c>
     </row>
     <row r="2070">
@@ -21127,7 +21127,7 @@
         </is>
       </c>
       <c r="B2070" t="n">
-        <v>910.6794098433452</v>
+        <v>1405.97548635336</v>
       </c>
     </row>
     <row r="2071">
@@ -21137,7 +21137,7 @@
         </is>
       </c>
       <c r="B2071" t="n">
-        <v>935.7385161906998</v>
+        <v>1402.320365714729</v>
       </c>
     </row>
     <row r="2072">
@@ -21147,7 +21147,7 @@
         </is>
       </c>
       <c r="B2072" t="n">
-        <v>1426.210217318263</v>
+        <v>1926.673767969866</v>
       </c>
     </row>
     <row r="2073">
@@ -21157,7 +21157,7 @@
         </is>
       </c>
       <c r="B2073" t="n">
-        <v>924.496739165696</v>
+        <v>1446.020144998062</v>
       </c>
     </row>
     <row r="2074">
@@ -21167,7 +21167,7 @@
         </is>
       </c>
       <c r="B2074" t="n">
-        <v>1167.46249978852</v>
+        <v>1814.554999577041</v>
       </c>
     </row>
     <row r="2075">
@@ -21177,7 +21177,7 @@
         </is>
       </c>
       <c r="B2075" t="n">
-        <v>1168.389797707694</v>
+        <v>1980.082928748727</v>
       </c>
     </row>
     <row r="2076">
@@ -21187,7 +21187,7 @@
         </is>
       </c>
       <c r="B2076" t="n">
-        <v>1167.471339452481</v>
+        <v>2252.369345571633</v>
       </c>
     </row>
     <row r="2077">
@@ -21197,7 +21197,7 @@
         </is>
       </c>
       <c r="B2077" t="n">
-        <v>1296.956368969697</v>
+        <v>2437.279404606063</v>
       </c>
     </row>
     <row r="2078">
@@ -21207,7 +21207,7 @@
         </is>
       </c>
       <c r="B2078" t="n">
-        <v>961.3907268380058</v>
+        <v>2037.484787009342</v>
       </c>
     </row>
     <row r="2079">
@@ -21217,7 +21217,7 @@
         </is>
       </c>
       <c r="B2079" t="n">
-        <v>1124.056356362371</v>
+        <v>2152.956046058083</v>
       </c>
     </row>
     <row r="2080">
@@ -21227,7 +21227,7 @@
         </is>
       </c>
       <c r="B2080" t="n">
-        <v>1068.808270178402</v>
+        <v>2194.023207023464</v>
       </c>
     </row>
     <row r="2081">
@@ -21237,7 +21237,7 @@
         </is>
       </c>
       <c r="B2081" t="n">
-        <v>923.4818144174862</v>
+        <v>1841.243628834972</v>
       </c>
     </row>
     <row r="2082">
@@ -21247,7 +21247,7 @@
         </is>
       </c>
       <c r="B2082" t="n">
-        <v>696.6734146006492</v>
+        <v>1414.317591243656</v>
       </c>
     </row>
     <row r="2083">
@@ -21257,7 +21257,7 @@
         </is>
       </c>
       <c r="B2083" t="n">
-        <v>544.0751097850379</v>
+        <v>1126.859120489281</v>
       </c>
     </row>
     <row r="2084">
@@ -21267,7 +21267,7 @@
         </is>
       </c>
       <c r="B2084" t="n">
-        <v>458.9299291657027</v>
+        <v>942.8757458471114</v>
       </c>
     </row>
     <row r="2085">
@@ -21277,7 +21277,7 @@
         </is>
       </c>
       <c r="B2085" t="n">
-        <v>446.8178603210105</v>
+        <v>903.1813530230415</v>
       </c>
     </row>
     <row r="2086">
@@ -21287,7 +21287,7 @@
         </is>
       </c>
       <c r="B2086" t="n">
-        <v>438.329487449065</v>
+        <v>1007.143771237279</v>
       </c>
     </row>
     <row r="2087">
@@ -21297,7 +21297,7 @@
         </is>
       </c>
       <c r="B2087" t="n">
-        <v>533.5772191594974</v>
+        <v>1118.484438319005</v>
       </c>
     </row>
     <row r="2088">
@@ -21307,7 +21307,7 @@
         </is>
       </c>
       <c r="B2088" t="n">
-        <v>201.7619753086423</v>
+        <v>508.1696986671141</v>
       </c>
     </row>
     <row r="2089">
@@ -21327,7 +21327,7 @@
         </is>
       </c>
       <c r="B2090" t="n">
-        <v>98.34386551224328</v>
+        <v>179.3384959552418</v>
       </c>
     </row>
     <row r="2091">
@@ -21337,7 +21337,7 @@
         </is>
       </c>
       <c r="B2091" t="n">
-        <v>64.05074995334846</v>
+        <v>146.1991100017849</v>
       </c>
     </row>
     <row r="2092">
@@ -21347,7 +21347,7 @@
         </is>
       </c>
       <c r="B2092" t="n">
-        <v>58.93982728577206</v>
+        <v>139.0069572165215</v>
       </c>
     </row>
     <row r="2093">
@@ -21357,7 +21357,7 @@
         </is>
       </c>
       <c r="B2093" t="n">
-        <v>94.20316203207703</v>
+        <v>173.4218844994399</v>
       </c>
     </row>
     <row r="2094">
@@ -21367,7 +21367,7 @@
         </is>
       </c>
       <c r="B2094" t="n">
-        <v>114.0195177735077</v>
+        <v>194.2790643840002</v>
       </c>
     </row>
     <row r="2095">
@@ -21377,7 +21377,7 @@
         </is>
       </c>
       <c r="B2095" t="n">
-        <v>112.8243346914115</v>
+        <v>194.4691348409178</v>
       </c>
     </row>
     <row r="2096">
@@ -21387,7 +21387,7 @@
         </is>
       </c>
       <c r="B2096" t="n">
-        <v>147.6900747466941</v>
+        <v>228.780128979891</v>
       </c>
     </row>
     <row r="2097">
@@ -21397,7 +21397,7 @@
         </is>
       </c>
       <c r="B2097" t="n">
-        <v>64.26561023528546</v>
+        <v>146.390646034048</v>
       </c>
     </row>
     <row r="2098">
@@ -21407,7 +21407,7 @@
         </is>
       </c>
       <c r="B2098" t="n">
-        <v>123.4649141795089</v>
+        <v>208.5827021482051</v>
       </c>
     </row>
     <row r="2099">
@@ -21417,7 +21417,7 @@
         </is>
       </c>
       <c r="B2099" t="n">
-        <v>102.5546366812723</v>
+        <v>191.3540354679297</v>
       </c>
     </row>
     <row r="2100">
@@ -21427,7 +21427,7 @@
         </is>
       </c>
       <c r="B2100" t="n">
-        <v>75.5014537061889</v>
+        <v>166.3298680260996</v>
       </c>
     </row>
     <row r="2101">
@@ -21437,7 +21437,7 @@
         </is>
       </c>
       <c r="B2101" t="n">
-        <v>11.9561783952062</v>
+        <v>107.5476463422644</v>
       </c>
     </row>
     <row r="2102">
@@ -21447,7 +21447,7 @@
         </is>
       </c>
       <c r="B2102" t="n">
-        <v>0</v>
+        <v>37.14264185076137</v>
       </c>
     </row>
     <row r="2103">
@@ -21457,7 +21457,7 @@
         </is>
       </c>
       <c r="B2103" t="n">
-        <v>12.77281400011317</v>
+        <v>96.39880363305186</v>
       </c>
     </row>
     <row r="2104">
@@ -21467,7 +21467,7 @@
         </is>
       </c>
       <c r="B2104" t="n">
-        <v>78.06666291131526</v>
+        <v>169.9876083218709</v>
       </c>
     </row>
     <row r="2105">
@@ -21477,7 +21477,7 @@
         </is>
       </c>
       <c r="B2105" t="n">
-        <v>2.998991354138272</v>
+        <v>20.41778782589695</v>
       </c>
     </row>
     <row r="2106">
@@ -21487,7 +21487,7 @@
         </is>
       </c>
       <c r="B2106" t="n">
-        <v>31.70128564549083</v>
+        <v>85.38216314121131</v>
       </c>
     </row>
     <row r="2107">
@@ -21497,7 +21497,7 @@
         </is>
       </c>
       <c r="B2107" t="n">
-        <v>70.06888287373215</v>
+        <v>96.04501294625359</v>
       </c>
     </row>
     <row r="2108">
@@ -21507,7 +21507,7 @@
         </is>
       </c>
       <c r="B2108" t="n">
-        <v>96.22372290881719</v>
+        <v>53.03194194096077</v>
       </c>
     </row>
     <row r="2109">
@@ -21517,7 +21517,7 @@
         </is>
       </c>
       <c r="B2109" t="n">
-        <v>88.40718380948954</v>
+        <v>96.04945026281951</v>
       </c>
     </row>
     <row r="2110">
@@ -21527,7 +21527,7 @@
         </is>
       </c>
       <c r="B2110" t="n">
-        <v>40.14856388189092</v>
+        <v>129.0618909555228</v>
       </c>
     </row>
     <row r="2111">
@@ -21537,7 +21537,7 @@
         </is>
       </c>
       <c r="B2111" t="n">
-        <v>0</v>
+        <v>81.15498215798914</v>
       </c>
     </row>
     <row r="2112">
@@ -21547,7 +21547,7 @@
         </is>
       </c>
       <c r="B2112" t="n">
-        <v>150.7456659606139</v>
+        <v>53.2369279322215</v>
       </c>
     </row>
     <row r="2113">
@@ -22047,7 +22047,7 @@
         </is>
       </c>
       <c r="B2162" t="n">
-        <v>495.8228198046791</v>
+        <v>638.8094943175111</v>
       </c>
     </row>
     <row r="2163">
@@ -22057,7 +22057,7 @@
         </is>
       </c>
       <c r="B2163" t="n">
-        <v>455.6192176476661</v>
+        <v>600.642668656252</v>
       </c>
     </row>
     <row r="2164">
@@ -22067,7 +22067,7 @@
         </is>
       </c>
       <c r="B2164" t="n">
-        <v>432.3494074496289</v>
+        <v>573.698686827375</v>
       </c>
     </row>
     <row r="2165">
@@ -22077,7 +22077,7 @@
         </is>
       </c>
       <c r="B2165" t="n">
-        <v>509.635427266736</v>
+        <v>649.4869411610421</v>
       </c>
     </row>
     <row r="2166">
@@ -22087,7 +22087,7 @@
         </is>
       </c>
       <c r="B2166" t="n">
-        <v>476.2477056035</v>
+        <v>617.936674427408</v>
       </c>
     </row>
     <row r="2167">
@@ -22097,7 +22097,7 @@
         </is>
       </c>
       <c r="B2167" t="n">
-        <v>480.2705327479183</v>
+        <v>624.4050068580082</v>
       </c>
     </row>
     <row r="2168">
@@ -22107,7 +22107,7 @@
         </is>
       </c>
       <c r="B2168" t="n">
-        <v>488.115209251393</v>
+        <v>631.270343455383</v>
       </c>
     </row>
     <row r="2169">
@@ -22117,7 +22117,7 @@
         </is>
       </c>
       <c r="B2169" t="n">
-        <v>538.203391980632</v>
+        <v>683.1856667176781</v>
       </c>
     </row>
     <row r="2170">
@@ -22127,7 +22127,7 @@
         </is>
       </c>
       <c r="B2170" t="n">
-        <v>575.5014445850218</v>
+        <v>725.7670779605279</v>
       </c>
     </row>
     <row r="2171">
@@ -22137,7 +22137,7 @@
         </is>
       </c>
       <c r="B2171" t="n">
-        <v>583.2711653874157</v>
+        <v>740.036257860784</v>
       </c>
     </row>
     <row r="2172">
@@ -22147,7 +22147,7 @@
         </is>
       </c>
       <c r="B2172" t="n">
-        <v>605.99028426717</v>
+        <v>766.33736954732</v>
       </c>
     </row>
     <row r="2173">
@@ -22157,7 +22157,7 @@
         </is>
       </c>
       <c r="B2173" t="n">
-        <v>533.6833086335109</v>
+        <v>702.4390155092791</v>
       </c>
     </row>
     <row r="2174">
@@ -22167,7 +22167,7 @@
         </is>
       </c>
       <c r="B2174" t="n">
-        <v>564.8286691655238</v>
+        <v>734.8256699151821</v>
       </c>
     </row>
     <row r="2175">
@@ -22177,7 +22177,7 @@
         </is>
       </c>
       <c r="B2175" t="n">
-        <v>526.3500685648388</v>
+        <v>696.4175177057189</v>
       </c>
     </row>
     <row r="2176">
@@ -22187,7 +22187,7 @@
         </is>
       </c>
       <c r="B2176" t="n">
-        <v>574.2979809599209</v>
+        <v>736.5738038193249</v>
       </c>
     </row>
     <row r="2177">
@@ -22197,7 +22197,7 @@
         </is>
       </c>
       <c r="B2177" t="n">
-        <v>476.9132296921041</v>
+        <v>644.0654557425922</v>
       </c>
     </row>
     <row r="2178">
@@ -22207,7 +22207,7 @@
         </is>
       </c>
       <c r="B2178" t="n">
-        <v>513.2773245900582</v>
+        <v>674.4030933956481</v>
       </c>
     </row>
     <row r="2179">
@@ -22217,7 +22217,7 @@
         </is>
       </c>
       <c r="B2179" t="n">
-        <v>549.7516171439289</v>
+        <v>708.534388001393</v>
       </c>
     </row>
     <row r="2180">
@@ -22227,7 +22227,7 @@
         </is>
       </c>
       <c r="B2180" t="n">
-        <v>512.927721586315</v>
+        <v>670.023152347925</v>
       </c>
     </row>
     <row r="2181">
@@ -22237,7 +22237,7 @@
         </is>
       </c>
       <c r="B2181" t="n">
-        <v>493.8745708479591</v>
+        <v>651.2500278166331</v>
       </c>
     </row>
     <row r="2182">
@@ -22247,7 +22247,7 @@
         </is>
       </c>
       <c r="B2182" t="n">
-        <v>466.6004466805521</v>
+        <v>623.5666663990022</v>
       </c>
     </row>
     <row r="2183">
@@ -22257,7 +22257,7 @@
         </is>
       </c>
       <c r="B2183" t="n">
-        <v>455.64185915526</v>
+        <v>605.183159758982</v>
       </c>
     </row>
     <row r="2184">
@@ -22267,7 +22267,7 @@
         </is>
       </c>
       <c r="B2184" t="n">
-        <v>451.7321120035901</v>
+        <v>598.550259890382</v>
       </c>
     </row>
     <row r="2185">
@@ -22287,7 +22287,7 @@
         </is>
       </c>
       <c r="B2186" t="n">
-        <v>42.80058682395723</v>
+        <v>255.4728341417388</v>
       </c>
     </row>
     <row r="2187">
@@ -22297,7 +22297,7 @@
         </is>
       </c>
       <c r="B2187" t="n">
-        <v>-0</v>
+        <v>177.6710016304023</v>
       </c>
     </row>
     <row r="2188">
@@ -22307,7 +22307,7 @@
         </is>
       </c>
       <c r="B2188" t="n">
-        <v>41.78112789908552</v>
+        <v>250.8335459216281</v>
       </c>
     </row>
     <row r="2189">
@@ -22317,7 +22317,7 @@
         </is>
       </c>
       <c r="B2189" t="n">
-        <v>44.38836975747182</v>
+        <v>240.2251222309933</v>
       </c>
     </row>
     <row r="2190">
@@ -22327,7 +22327,7 @@
         </is>
       </c>
       <c r="B2190" t="n">
-        <v>206.0808942753935</v>
+        <v>408.7853996618996</v>
       </c>
     </row>
     <row r="2191">
@@ -22337,7 +22337,7 @@
         </is>
       </c>
       <c r="B2191" t="n">
-        <v>203.2596828607619</v>
+        <v>394.2126249807814</v>
       </c>
     </row>
     <row r="2192">
@@ -22347,7 +22347,7 @@
         </is>
       </c>
       <c r="B2192" t="n">
-        <v>389.2200210382766</v>
+        <v>594.0393630642102</v>
       </c>
     </row>
     <row r="2193">
@@ -22357,7 +22357,7 @@
         </is>
       </c>
       <c r="B2193" t="n">
-        <v>154.7452580659607</v>
+        <v>368.1835408232809</v>
       </c>
     </row>
     <row r="2194">
@@ -22367,7 +22367,7 @@
         </is>
       </c>
       <c r="B2194" t="n">
-        <v>241.495047752956</v>
+        <v>506.3236448886282</v>
       </c>
     </row>
     <row r="2195">
@@ -22377,7 +22377,7 @@
         </is>
       </c>
       <c r="B2195" t="n">
-        <v>225.4925344939508</v>
+        <v>557.6854640496332</v>
       </c>
     </row>
     <row r="2196">
@@ -22387,7 +22387,7 @@
         </is>
       </c>
       <c r="B2196" t="n">
-        <v>213.8873074425895</v>
+        <v>657.8918617987608</v>
       </c>
     </row>
     <row r="2197">
@@ -22397,7 +22397,7 @@
         </is>
       </c>
       <c r="B2197" t="n">
-        <v>264.2807238437707</v>
+        <v>730.9684847245798</v>
       </c>
     </row>
     <row r="2198">
@@ -22407,7 +22407,7 @@
         </is>
       </c>
       <c r="B2198" t="n">
-        <v>95.30552341317801</v>
+        <v>562.4177862883913</v>
       </c>
     </row>
     <row r="2199">
@@ -22417,7 +22417,7 @@
         </is>
       </c>
       <c r="B2199" t="n">
-        <v>186.4610862710928</v>
+        <v>613.2864990966104</v>
       </c>
     </row>
     <row r="2200">
@@ -22427,7 +22427,7 @@
         </is>
       </c>
       <c r="B2200" t="n">
-        <v>166.5933105730128</v>
+        <v>627.097942133677</v>
       </c>
     </row>
     <row r="2201">
@@ -22437,7 +22437,7 @@
         </is>
       </c>
       <c r="B2201" t="n">
-        <v>74.0031810158044</v>
+        <v>484.4953987145593</v>
       </c>
     </row>
     <row r="2202">
@@ -22447,7 +22447,7 @@
         </is>
       </c>
       <c r="B2202" t="n">
-        <v>-0</v>
+        <v>309.5918907373726</v>
       </c>
     </row>
     <row r="2203">
@@ -22457,7 +22457,7 @@
         </is>
       </c>
       <c r="B2203" t="n">
-        <v>-0</v>
+        <v>194.6030474595022</v>
       </c>
     </row>
     <row r="2204">
@@ -22467,7 +22467,7 @@
         </is>
       </c>
       <c r="B2204" t="n">
-        <v>-0</v>
+        <v>124.93650586212</v>
       </c>
     </row>
     <row r="2205">
@@ -22477,7 +22477,7 @@
         </is>
       </c>
       <c r="B2205" t="n">
-        <v>-0</v>
+        <v>115.5372759594299</v>
       </c>
     </row>
     <row r="2206">
@@ -22487,7 +22487,7 @@
         </is>
       </c>
       <c r="B2206" t="n">
-        <v>-0</v>
+        <v>163.951747117479</v>
       </c>
     </row>
     <row r="2207">
@@ -22497,7 +22497,7 @@
         </is>
       </c>
       <c r="B2207" t="n">
-        <v>-0</v>
+        <v>215.2198225959875</v>
       </c>
     </row>
     <row r="2208">
@@ -22507,7 +22507,7 @@
         </is>
       </c>
       <c r="B2208" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="2209">
@@ -23007,7 +23007,7 @@
         </is>
       </c>
       <c r="B2258" t="n">
-        <v>-180.8782424271247</v>
+        <v>-362.7563181875804</v>
       </c>
     </row>
     <row r="2259">
@@ -23017,7 +23017,7 @@
         </is>
       </c>
       <c r="B2259" t="n">
-        <v>-108.4165939979258</v>
+        <v>-296.1429991318825</v>
       </c>
     </row>
     <row r="2260">
@@ -23027,7 +23027,7 @@
         </is>
       </c>
       <c r="B2260" t="n">
-        <v>-177.4068846437128</v>
+        <v>-356.1892692874258</v>
       </c>
     </row>
     <row r="2261">
@@ -23037,7 +23037,7 @@
         </is>
       </c>
       <c r="B2261" t="n">
-        <v>-179.5307996266767</v>
+        <v>-347.0110992533534</v>
       </c>
     </row>
     <row r="2262">
@@ -23047,7 +23047,7 @@
         </is>
       </c>
       <c r="B2262" t="n">
-        <v>-318.7377934451708</v>
+        <v>-492.0914202236761</v>
       </c>
     </row>
     <row r="2263">
@@ -23057,7 +23057,7 @@
         </is>
       </c>
       <c r="B2263" t="n">
-        <v>-327.5084806667449</v>
+        <v>-490.8121280001553</v>
       </c>
     </row>
     <row r="2264">
@@ -23067,7 +23067,7 @@
         </is>
       </c>
       <c r="B2264" t="n">
-        <v>-499.1735760613921</v>
+        <v>-674.335818789453</v>
       </c>
     </row>
     <row r="2265">
@@ -23077,7 +23077,7 @@
         </is>
       </c>
       <c r="B2265" t="n">
-        <v>-323.5738587079936</v>
+        <v>-506.1070507493218</v>
       </c>
     </row>
     <row r="2266">
@@ -23087,7 +23087,7 @@
         </is>
       </c>
       <c r="B2266" t="n">
-        <v>-408.6118749259821</v>
+        <v>-635.0942498519643</v>
       </c>
     </row>
     <row r="2267">
@@ -23097,7 +23097,7 @@
         </is>
       </c>
       <c r="B2267" t="n">
-        <v>-408.9364291976927</v>
+        <v>-693.0290250620545</v>
       </c>
     </row>
     <row r="2268">
@@ -23107,7 +23107,7 @@
         </is>
       </c>
       <c r="B2268" t="n">
-        <v>-408.6149688083684</v>
+        <v>-788.3292709500715</v>
       </c>
     </row>
     <row r="2269">
@@ -23117,7 +23117,7 @@
         </is>
       </c>
       <c r="B2269" t="n">
-        <v>-453.9347291393938</v>
+        <v>-853.047791612122</v>
       </c>
     </row>
     <row r="2270">
@@ -23127,7 +23127,7 @@
         </is>
       </c>
       <c r="B2270" t="n">
-        <v>-336.486754393302</v>
+        <v>-713.1196754532696</v>
       </c>
     </row>
     <row r="2271">
@@ -23137,7 +23137,7 @@
         </is>
       </c>
       <c r="B2271" t="n">
-        <v>-393.4197247268299</v>
+        <v>-753.534616120329</v>
       </c>
     </row>
     <row r="2272">
@@ -23147,7 +23147,7 @@
         </is>
       </c>
       <c r="B2272" t="n">
-        <v>-374.0828945624409</v>
+        <v>-767.9081224582125</v>
       </c>
     </row>
     <row r="2273">
@@ -23157,7 +23157,7 @@
         </is>
       </c>
       <c r="B2273" t="n">
-        <v>-323.2186350461202</v>
+        <v>-644.4352700922402</v>
       </c>
     </row>
     <row r="2274">
@@ -23167,7 +23167,7 @@
         </is>
       </c>
       <c r="B2274" t="n">
-        <v>-243.8356951102272</v>
+        <v>-495.0111569352796</v>
       </c>
     </row>
     <row r="2275">
@@ -23177,7 +23177,7 @@
         </is>
       </c>
       <c r="B2275" t="n">
-        <v>-120.6921097850378</v>
+        <v>-394.4006921712485</v>
       </c>
     </row>
     <row r="2276">
@@ -23187,7 +23187,7 @@
         </is>
       </c>
       <c r="B2276" t="n">
-        <v>-44.48926249903565</v>
+        <v>-330.006511046489</v>
       </c>
     </row>
     <row r="2277">
@@ -23197,7 +23197,7 @@
         </is>
       </c>
       <c r="B2277" t="n">
-        <v>-43.25036032101042</v>
+        <v>-316.1134735580645</v>
       </c>
     </row>
     <row r="2278">
@@ -23207,7 +23207,7 @@
         </is>
       </c>
       <c r="B2278" t="n">
-        <v>-44.07998744906502</v>
+        <v>-352.5003199330476</v>
       </c>
     </row>
     <row r="2279">
@@ -23217,7 +23217,7 @@
         </is>
       </c>
       <c r="B2279" t="n">
-        <v>-148.3820524928304</v>
+        <v>-391.4695534116516</v>
       </c>
     </row>
     <row r="2280">
@@ -23227,7 +23227,7 @@
         </is>
       </c>
       <c r="B2280" t="n">
-        <v>70.61669135802477</v>
+        <v>-125.5410320004471</v>
       </c>
     </row>
     <row r="2281">
@@ -23247,7 +23247,7 @@
         </is>
       </c>
       <c r="B2282" t="n">
-        <v>34.42035292928516</v>
+        <v>62.76847358433463</v>
       </c>
     </row>
     <row r="2283">
@@ -23257,7 +23257,7 @@
         </is>
       </c>
       <c r="B2283" t="n">
-        <v>22.41776248367195</v>
+        <v>51.16968850062472</v>
       </c>
     </row>
     <row r="2284">
@@ -23267,7 +23267,7 @@
         </is>
       </c>
       <c r="B2284" t="n">
-        <v>20.62893955002021</v>
+        <v>48.65243502578255</v>
       </c>
     </row>
     <row r="2285">
@@ -23277,7 +23277,7 @@
         </is>
       </c>
       <c r="B2285" t="n">
-        <v>32.97110671122697</v>
+        <v>60.69765957480399</v>
       </c>
     </row>
     <row r="2286">
@@ -23287,7 +23287,7 @@
         </is>
       </c>
       <c r="B2286" t="n">
-        <v>39.90683122072771</v>
+        <v>67.99767253440011</v>
       </c>
     </row>
     <row r="2287">
@@ -23297,7 +23297,7 @@
         </is>
       </c>
       <c r="B2287" t="n">
-        <v>39.48851714199405</v>
+        <v>68.06419719432124</v>
       </c>
     </row>
     <row r="2288">
@@ -23307,7 +23307,7 @@
         </is>
       </c>
       <c r="B2288" t="n">
-        <v>51.69152616134293</v>
+        <v>80.07304514296183</v>
       </c>
     </row>
     <row r="2289">
@@ -23317,7 +23317,7 @@
         </is>
       </c>
       <c r="B2289" t="n">
-        <v>22.4929635823499</v>
+        <v>51.23672611191681</v>
       </c>
     </row>
     <row r="2290">
@@ -23327,7 +23327,7 @@
         </is>
       </c>
       <c r="B2290" t="n">
-        <v>43.21271996282811</v>
+        <v>73.00394575187178</v>
       </c>
     </row>
     <row r="2291">
@@ -23337,7 +23337,7 @@
         </is>
       </c>
       <c r="B2291" t="n">
-        <v>35.89412283844532</v>
+        <v>66.97391241377542</v>
       </c>
     </row>
     <row r="2292">
@@ -23347,7 +23347,7 @@
         </is>
       </c>
       <c r="B2292" t="n">
-        <v>26.42550879716612</v>
+        <v>58.21545380913484</v>
       </c>
     </row>
     <row r="2293">
@@ -23357,7 +23357,7 @@
         </is>
       </c>
       <c r="B2293" t="n">
-        <v>4.18466243832217</v>
+        <v>37.64167621979254</v>
       </c>
     </row>
     <row r="2294">
@@ -23367,7 +23367,7 @@
         </is>
       </c>
       <c r="B2294" t="n">
-        <v>0</v>
+        <v>12.99992464776648</v>
       </c>
     </row>
     <row r="2295">
@@ -23377,7 +23377,7 @@
         </is>
       </c>
       <c r="B2295" t="n">
-        <v>4.47048490003961</v>
+        <v>33.73958127156816</v>
       </c>
     </row>
     <row r="2296">
@@ -23387,7 +23387,7 @@
         </is>
       </c>
       <c r="B2296" t="n">
-        <v>27.32333201896034</v>
+        <v>59.49566291265482</v>
       </c>
     </row>
     <row r="2297">
@@ -23397,7 +23397,7 @@
         </is>
       </c>
       <c r="B2297" t="n">
-        <v>1.049646973948395</v>
+        <v>7.146225739063933</v>
       </c>
     </row>
     <row r="2298">
@@ -23407,7 +23407,7 @@
         </is>
       </c>
       <c r="B2298" t="n">
-        <v>11.09544997592179</v>
+        <v>29.88375709942397</v>
       </c>
     </row>
     <row r="2299">
@@ -23417,7 +23417,7 @@
         </is>
       </c>
       <c r="B2299" t="n">
-        <v>24.52410900580625</v>
+        <v>33.61575453118877</v>
       </c>
     </row>
     <row r="2300">
@@ -23427,7 +23427,7 @@
         </is>
       </c>
       <c r="B2300" t="n">
-        <v>33.67830301808604</v>
+        <v>18.56117967933627</v>
       </c>
     </row>
     <row r="2301">
@@ -23437,7 +23437,7 @@
         </is>
       </c>
       <c r="B2301" t="n">
-        <v>30.94251433332134</v>
+        <v>33.61730759198684</v>
       </c>
     </row>
     <row r="2302">
@@ -23447,7 +23447,7 @@
         </is>
       </c>
       <c r="B2302" t="n">
-        <v>14.05199735866182</v>
+        <v>45.17166183443299</v>
       </c>
     </row>
     <row r="2303">
@@ -23457,7 +23457,7 @@
         </is>
       </c>
       <c r="B2303" t="n">
-        <v>0</v>
+        <v>28.40424375529621</v>
       </c>
     </row>
     <row r="2304">
@@ -23467,7 +23467,7 @@
         </is>
       </c>
       <c r="B2304" t="n">
-        <v>52.76098308621486</v>
+        <v>18.63292477627753</v>
       </c>
     </row>
     <row r="2305">
@@ -23937,7 +23937,7 @@
         </is>
       </c>
       <c r="B2351" t="n">
-        <v>36.2894482740426</v>
+        <v>36.28944827404258</v>
       </c>
     </row>
     <row r="2352">
@@ -23967,7 +23967,7 @@
         </is>
       </c>
       <c r="B2354" t="n">
-        <v>-173.5379869316377</v>
+        <v>-223.5833230111289</v>
       </c>
     </row>
     <row r="2355">
@@ -23977,7 +23977,7 @@
         </is>
       </c>
       <c r="B2355" t="n">
-        <v>-159.4667261766831</v>
+        <v>-210.2249340296882</v>
       </c>
     </row>
     <row r="2356">
@@ -23987,7 +23987,7 @@
         </is>
       </c>
       <c r="B2356" t="n">
-        <v>-151.3222926073701</v>
+        <v>-200.7945403895812</v>
       </c>
     </row>
     <row r="2357">
@@ -23997,7 +23997,7 @@
         </is>
       </c>
       <c r="B2357" t="n">
-        <v>-178.3723995433576</v>
+        <v>-227.3204294063647</v>
       </c>
     </row>
     <row r="2358">
@@ -24007,7 +24007,7 @@
         </is>
       </c>
       <c r="B2358" t="n">
-        <v>-166.686696961225</v>
+        <v>-216.2778360495928</v>
       </c>
     </row>
     <row r="2359">
@@ -24017,7 +24017,7 @@
         </is>
       </c>
       <c r="B2359" t="n">
-        <v>-168.0946864617714</v>
+        <v>-218.5417524003028</v>
       </c>
     </row>
     <row r="2360">
@@ -24027,7 +24027,7 @@
         </is>
       </c>
       <c r="B2360" t="n">
-        <v>-170.8403232379875</v>
+        <v>-220.944620209384</v>
       </c>
     </row>
     <row r="2361">
@@ -24037,7 +24037,7 @@
         </is>
       </c>
       <c r="B2361" t="n">
-        <v>-188.3711871932212</v>
+        <v>-239.1149833511873</v>
       </c>
     </row>
     <row r="2362">
@@ -24047,7 +24047,7 @@
         </is>
       </c>
       <c r="B2362" t="n">
-        <v>-201.4255056047576</v>
+        <v>-254.0184772861847</v>
       </c>
     </row>
     <row r="2363">
@@ -24057,7 +24057,7 @@
         </is>
       </c>
       <c r="B2363" t="n">
-        <v>-204.1449078855955</v>
+        <v>-259.0126902512744</v>
       </c>
     </row>
     <row r="2364">
@@ -24067,7 +24067,7 @@
         </is>
       </c>
       <c r="B2364" t="n">
-        <v>-212.0965994935095</v>
+        <v>-268.218079341562</v>
       </c>
     </row>
     <row r="2365">
@@ -24077,7 +24077,7 @@
         </is>
       </c>
       <c r="B2365" t="n">
-        <v>-186.7891580217288</v>
+        <v>-245.8536554282476</v>
       </c>
     </row>
     <row r="2366">
@@ -24087,7 +24087,7 @@
         </is>
       </c>
       <c r="B2366" t="n">
-        <v>-197.6900342079333</v>
+        <v>-257.1889844703137</v>
       </c>
     </row>
     <row r="2367">
@@ -24097,7 +24097,7 @@
         </is>
       </c>
       <c r="B2367" t="n">
-        <v>-184.2225239976935</v>
+        <v>-243.7461311970016</v>
       </c>
     </row>
     <row r="2368">
@@ -24107,7 +24107,7 @@
         </is>
       </c>
       <c r="B2368" t="n">
-        <v>-201.0042933359723</v>
+        <v>-257.8008313367637</v>
       </c>
     </row>
     <row r="2369">
@@ -24117,7 +24117,7 @@
         </is>
       </c>
       <c r="B2369" t="n">
-        <v>-166.9196303922364</v>
+        <v>-225.4229095099073</v>
       </c>
     </row>
     <row r="2370">
@@ -24127,7 +24127,7 @@
         </is>
       </c>
       <c r="B2370" t="n">
-        <v>-176.8918053272342</v>
+        <v>-236.0410826884768</v>
       </c>
     </row>
     <row r="2371">
@@ -24137,7 +24137,7 @@
         </is>
       </c>
       <c r="B2371" t="n">
-        <v>-119.0118742012418</v>
+        <v>-247.9870358004875</v>
       </c>
     </row>
     <row r="2372">
@@ -24147,7 +24147,7 @@
         </is>
       </c>
       <c r="B2372" t="n">
-        <v>-27.85010389954843</v>
+        <v>-234.5081033217737</v>
       </c>
     </row>
     <row r="2373">
@@ -24157,7 +24157,7 @@
         </is>
       </c>
       <c r="B2373" t="n">
-        <v>-79.33155352234378</v>
+        <v>-227.9375097358215</v>
       </c>
     </row>
     <row r="2374">
@@ -24167,7 +24167,7 @@
         </is>
       </c>
       <c r="B2374" t="n">
-        <v>-163.3101563381932</v>
+        <v>-218.2483332396508</v>
       </c>
     </row>
     <row r="2375">
@@ -24177,7 +24177,7 @@
         </is>
       </c>
       <c r="B2375" t="n">
-        <v>-155.3981473382142</v>
+        <v>-211.8141059156437</v>
       </c>
     </row>
     <row r="2376">
@@ -24187,7 +24187,7 @@
         </is>
       </c>
       <c r="B2376" t="n">
-        <v>49.21683381273854</v>
+        <v>-209.4925909616337</v>
       </c>
     </row>
     <row r="2377">
@@ -24207,7 +24207,7 @@
         </is>
       </c>
       <c r="B2378" t="n">
-        <v>14.98020538838503</v>
+        <v>89.41549194960859</v>
       </c>
     </row>
     <row r="2379">
@@ -24217,7 +24217,7 @@
         </is>
       </c>
       <c r="B2379" t="n">
-        <v>0</v>
+        <v>62.1848505706408</v>
       </c>
     </row>
     <row r="2380">
@@ -24227,7 +24227,7 @@
         </is>
       </c>
       <c r="B2380" t="n">
-        <v>14.62339476467994</v>
+        <v>87.79174107256986</v>
       </c>
     </row>
     <row r="2381">
@@ -24237,7 +24237,7 @@
         </is>
       </c>
       <c r="B2381" t="n">
-        <v>15.53592941511514</v>
+        <v>84.07879278084769</v>
       </c>
     </row>
     <row r="2382">
@@ -24247,7 +24247,7 @@
         </is>
       </c>
       <c r="B2382" t="n">
-        <v>72.12831299638773</v>
+        <v>143.0748898816649</v>
       </c>
     </row>
     <row r="2383">
@@ -24257,7 +24257,7 @@
         </is>
       </c>
       <c r="B2383" t="n">
-        <v>71.14088900126669</v>
+        <v>137.9744187432735</v>
       </c>
     </row>
     <row r="2384">
@@ -24267,7 +24267,7 @@
         </is>
       </c>
       <c r="B2384" t="n">
-        <v>136.2270073633968</v>
+        <v>207.9137770724736</v>
       </c>
     </row>
     <row r="2385">
@@ -24277,7 +24277,7 @@
         </is>
       </c>
       <c r="B2385" t="n">
-        <v>54.16084032308626</v>
+        <v>128.8642392881484</v>
       </c>
     </row>
     <row r="2386">
@@ -24287,7 +24287,7 @@
         </is>
       </c>
       <c r="B2386" t="n">
-        <v>84.52326671353461</v>
+        <v>177.2132757110199</v>
       </c>
     </row>
     <row r="2387">
@@ -24297,7 +24297,7 @@
         </is>
       </c>
       <c r="B2387" t="n">
-        <v>78.9223870728828</v>
+        <v>195.1899124173717</v>
       </c>
     </row>
     <row r="2388">
@@ -24307,7 +24307,7 @@
         </is>
       </c>
       <c r="B2388" t="n">
-        <v>74.86055760490632</v>
+        <v>230.2621516295663</v>
       </c>
     </row>
     <row r="2389">
@@ -24317,7 +24317,7 @@
         </is>
       </c>
       <c r="B2389" t="n">
-        <v>92.49825334531977</v>
+        <v>255.838969653603</v>
       </c>
     </row>
     <row r="2390">
@@ -24327,7 +24327,7 @@
         </is>
       </c>
       <c r="B2390" t="n">
-        <v>33.35693319461231</v>
+        <v>196.8462252009369</v>
       </c>
     </row>
     <row r="2391">
@@ -24337,7 +24337,7 @@
         </is>
       </c>
       <c r="B2391" t="n">
-        <v>65.26138019488249</v>
+        <v>214.6502746838137</v>
       </c>
     </row>
     <row r="2392">
@@ -24347,7 +24347,7 @@
         </is>
       </c>
       <c r="B2392" t="n">
-        <v>58.3076587005545</v>
+        <v>219.484279746787</v>
       </c>
     </row>
     <row r="2393">
@@ -24357,7 +24357,7 @@
         </is>
       </c>
       <c r="B2393" t="n">
-        <v>25.90111335553155</v>
+        <v>169.5733895500958</v>
       </c>
     </row>
     <row r="2394">
@@ -24367,7 +24367,7 @@
         </is>
       </c>
       <c r="B2394" t="n">
-        <v>0</v>
+        <v>108.3571617580804</v>
       </c>
     </row>
     <row r="2395">
@@ -24377,7 +24377,7 @@
         </is>
       </c>
       <c r="B2395" t="n">
-        <v>0</v>
+        <v>68.11106661082576</v>
       </c>
     </row>
     <row r="2396">
@@ -24387,7 +24387,7 @@
         </is>
       </c>
       <c r="B2396" t="n">
-        <v>0</v>
+        <v>43.72777705174201</v>
       </c>
     </row>
     <row r="2397">
@@ -24397,7 +24397,7 @@
         </is>
       </c>
       <c r="B2397" t="n">
-        <v>0</v>
+        <v>40.43804658580048</v>
       </c>
     </row>
     <row r="2398">
@@ -24407,7 +24407,7 @@
         </is>
       </c>
       <c r="B2398" t="n">
-        <v>0</v>
+        <v>57.38311149111766</v>
       </c>
     </row>
     <row r="2399">
@@ -24417,7 +24417,7 @@
         </is>
       </c>
       <c r="B2399" t="n">
-        <v>0</v>
+        <v>75.32693790859562</v>
       </c>
     </row>
     <row r="2400">
@@ -24927,7 +24927,7 @@
         </is>
       </c>
       <c r="B2450" t="n">
-        <v>180.8782424271247</v>
+        <v>362.7563181875804</v>
       </c>
     </row>
     <row r="2451">
@@ -24937,7 +24937,7 @@
         </is>
       </c>
       <c r="B2451" t="n">
-        <v>131.674582899274</v>
+        <v>296.1429991318825</v>
       </c>
     </row>
     <row r="2452">
@@ -24947,7 +24947,7 @@
         </is>
       </c>
       <c r="B2452" t="n">
-        <v>177.4068846437128</v>
+        <v>356.1892692874258</v>
       </c>
     </row>
     <row r="2453">
@@ -24957,7 +24957,7 @@
         </is>
       </c>
       <c r="B2453" t="n">
-        <v>179.5307996266767</v>
+        <v>347.0110992533534</v>
       </c>
     </row>
     <row r="2454">
@@ -24967,7 +24967,7 @@
         </is>
       </c>
       <c r="B2454" t="n">
-        <v>318.7377934451708</v>
+        <v>492.0914202236761</v>
       </c>
     </row>
     <row r="2455">
@@ -24977,7 +24977,7 @@
         </is>
       </c>
       <c r="B2455" t="n">
-        <v>327.5084806667449</v>
+        <v>490.8121280001553</v>
       </c>
     </row>
     <row r="2456">
@@ -24987,7 +24987,7 @@
         </is>
       </c>
       <c r="B2456" t="n">
-        <v>499.1735760613921</v>
+        <v>674.335818789453</v>
       </c>
     </row>
     <row r="2457">
@@ -24997,7 +24997,7 @@
         </is>
       </c>
       <c r="B2457" t="n">
-        <v>323.5738587079936</v>
+        <v>506.1070507493218</v>
       </c>
     </row>
     <row r="2458">
@@ -25007,7 +25007,7 @@
         </is>
       </c>
       <c r="B2458" t="n">
-        <v>408.6118749259821</v>
+        <v>635.0942498519643</v>
       </c>
     </row>
     <row r="2459">
@@ -25017,7 +25017,7 @@
         </is>
       </c>
       <c r="B2459" t="n">
-        <v>408.9364291976927</v>
+        <v>693.0290250620545</v>
       </c>
     </row>
     <row r="2460">
@@ -25027,7 +25027,7 @@
         </is>
       </c>
       <c r="B2460" t="n">
-        <v>408.6149688083684</v>
+        <v>788.3292709500715</v>
       </c>
     </row>
     <row r="2461">
@@ -25037,7 +25037,7 @@
         </is>
       </c>
       <c r="B2461" t="n">
-        <v>453.9347291393938</v>
+        <v>853.047791612122</v>
       </c>
     </row>
     <row r="2462">
@@ -25047,7 +25047,7 @@
         </is>
       </c>
       <c r="B2462" t="n">
-        <v>336.486754393302</v>
+        <v>713.1196754532696</v>
       </c>
     </row>
     <row r="2463">
@@ -25057,7 +25057,7 @@
         </is>
       </c>
       <c r="B2463" t="n">
-        <v>393.4197247268299</v>
+        <v>753.534616120329</v>
       </c>
     </row>
     <row r="2464">
@@ -25067,7 +25067,7 @@
         </is>
       </c>
       <c r="B2464" t="n">
-        <v>374.0828945624409</v>
+        <v>767.9081224582125</v>
       </c>
     </row>
     <row r="2465">
@@ -25077,7 +25077,7 @@
         </is>
       </c>
       <c r="B2465" t="n">
-        <v>323.2186350461202</v>
+        <v>644.4352700922402</v>
       </c>
     </row>
     <row r="2466">
@@ -25087,7 +25087,7 @@
         </is>
       </c>
       <c r="B2466" t="n">
-        <v>243.8356951102272</v>
+        <v>495.0111569352796</v>
       </c>
     </row>
     <row r="2467">
@@ -25097,7 +25097,7 @@
         </is>
       </c>
       <c r="B2467" t="n">
-        <v>190.4262884247632</v>
+        <v>394.4006921712485</v>
       </c>
     </row>
     <row r="2468">
@@ -25107,7 +25107,7 @@
         </is>
       </c>
       <c r="B2468" t="n">
-        <v>160.6254752079959</v>
+        <v>330.006511046489</v>
       </c>
     </row>
     <row r="2469">
@@ -25117,7 +25117,7 @@
         </is>
       </c>
       <c r="B2469" t="n">
-        <v>156.3862511123536</v>
+        <v>316.1134735580645</v>
       </c>
     </row>
     <row r="2470">
@@ -25127,7 +25127,7 @@
         </is>
       </c>
       <c r="B2470" t="n">
-        <v>153.4153206071728</v>
+        <v>352.5003199330476</v>
       </c>
     </row>
     <row r="2471">
@@ -25137,7 +25137,7 @@
         </is>
       </c>
       <c r="B2471" t="n">
-        <v>186.7520267058241</v>
+        <v>391.4695534116516</v>
       </c>
     </row>
     <row r="2472">
@@ -25147,7 +25147,7 @@
         </is>
       </c>
       <c r="B2472" t="n">
-        <v>70.61669135802478</v>
+        <v>177.8593945334899</v>
       </c>
     </row>
     <row r="2473">
@@ -25167,7 +25167,7 @@
         </is>
       </c>
       <c r="B2474" t="n">
-        <v>34.42035292928514</v>
+        <v>62.76847358433462</v>
       </c>
     </row>
     <row r="2475">
@@ -25177,7 +25177,7 @@
         </is>
       </c>
       <c r="B2475" t="n">
-        <v>22.41776248367196</v>
+        <v>51.16968850062472</v>
       </c>
     </row>
     <row r="2476">
@@ -25187,7 +25187,7 @@
         </is>
       </c>
       <c r="B2476" t="n">
-        <v>20.62893955002022</v>
+        <v>48.65243502578252</v>
       </c>
     </row>
     <row r="2477">
@@ -25197,7 +25197,7 @@
         </is>
       </c>
       <c r="B2477" t="n">
-        <v>32.97110671122696</v>
+        <v>60.69765957480397</v>
       </c>
     </row>
     <row r="2478">
@@ -25207,7 +25207,7 @@
         </is>
       </c>
       <c r="B2478" t="n">
-        <v>39.90683122072771</v>
+        <v>67.99767253440008</v>
       </c>
     </row>
     <row r="2479">
@@ -25217,7 +25217,7 @@
         </is>
       </c>
       <c r="B2479" t="n">
-        <v>39.48851714199402</v>
+        <v>68.06419719432124</v>
       </c>
     </row>
     <row r="2480">
@@ -25227,7 +25227,7 @@
         </is>
       </c>
       <c r="B2480" t="n">
-        <v>51.69152616134291</v>
+        <v>80.07304514296185</v>
       </c>
     </row>
     <row r="2481">
@@ -25237,7 +25237,7 @@
         </is>
       </c>
       <c r="B2481" t="n">
-        <v>22.49296358234991</v>
+        <v>51.23672611191678</v>
       </c>
     </row>
     <row r="2482">
@@ -25247,7 +25247,7 @@
         </is>
       </c>
       <c r="B2482" t="n">
-        <v>43.21271996282812</v>
+        <v>73.00394575187178</v>
       </c>
     </row>
     <row r="2483">
@@ -25257,7 +25257,7 @@
         </is>
       </c>
       <c r="B2483" t="n">
-        <v>35.89412283844531</v>
+        <v>66.97391241377539</v>
       </c>
     </row>
     <row r="2484">
@@ -25267,7 +25267,7 @@
         </is>
       </c>
       <c r="B2484" t="n">
-        <v>26.42550879716611</v>
+        <v>58.21545380913486</v>
       </c>
     </row>
     <row r="2485">
@@ -25277,7 +25277,7 @@
         </is>
       </c>
       <c r="B2485" t="n">
-        <v>4.184662438322169</v>
+        <v>37.64167621979255</v>
       </c>
     </row>
     <row r="2486">
@@ -25287,7 +25287,7 @@
         </is>
       </c>
       <c r="B2486" t="n">
-        <v>0</v>
+        <v>12.99992464776648</v>
       </c>
     </row>
     <row r="2487">
@@ -25297,7 +25297,7 @@
         </is>
       </c>
       <c r="B2487" t="n">
-        <v>4.470484900039608</v>
+        <v>33.73958127156815</v>
       </c>
     </row>
     <row r="2488">
@@ -25307,7 +25307,7 @@
         </is>
       </c>
       <c r="B2488" t="n">
-        <v>27.32333201896034</v>
+        <v>59.4956629126548</v>
       </c>
     </row>
     <row r="2489">
@@ -25317,7 +25317,7 @@
         </is>
       </c>
       <c r="B2489" t="n">
-        <v>1.049646973948395</v>
+        <v>7.146225739063931</v>
       </c>
     </row>
     <row r="2490">
@@ -25327,7 +25327,7 @@
         </is>
       </c>
       <c r="B2490" t="n">
-        <v>11.09544997592179</v>
+        <v>29.88375709942396</v>
       </c>
     </row>
     <row r="2491">
@@ -25337,7 +25337,7 @@
         </is>
       </c>
       <c r="B2491" t="n">
-        <v>24.52410900580625</v>
+        <v>33.61575453118876</v>
       </c>
     </row>
     <row r="2492">
@@ -25347,7 +25347,7 @@
         </is>
       </c>
       <c r="B2492" t="n">
-        <v>33.67830301808604</v>
+        <v>18.56117967933627</v>
       </c>
     </row>
     <row r="2493">
@@ -25357,7 +25357,7 @@
         </is>
       </c>
       <c r="B2493" t="n">
-        <v>30.94251433332134</v>
+        <v>33.61730759198682</v>
       </c>
     </row>
     <row r="2494">
@@ -25367,7 +25367,7 @@
         </is>
       </c>
       <c r="B2494" t="n">
-        <v>14.05199735866182</v>
+        <v>45.17166183443297</v>
       </c>
     </row>
     <row r="2495">
@@ -25377,7 +25377,7 @@
         </is>
       </c>
       <c r="B2495" t="n">
-        <v>0</v>
+        <v>28.4042437552962</v>
       </c>
     </row>
     <row r="2496">
@@ -25387,7 +25387,7 @@
         </is>
       </c>
       <c r="B2496" t="n">
-        <v>52.76098308621486</v>
+        <v>18.63292477627752</v>
       </c>
     </row>
     <row r="2497">
@@ -25887,7 +25887,7 @@
         </is>
       </c>
       <c r="B2546" t="n">
-        <v>173.5379869316377</v>
+        <v>223.5833230111289</v>
       </c>
     </row>
     <row r="2547">
@@ -25897,7 +25897,7 @@
         </is>
       </c>
       <c r="B2547" t="n">
-        <v>159.4667261766831</v>
+        <v>210.2249340296882</v>
       </c>
     </row>
     <row r="2548">
@@ -25907,7 +25907,7 @@
         </is>
       </c>
       <c r="B2548" t="n">
-        <v>151.3222926073701</v>
+        <v>200.7945403895812</v>
       </c>
     </row>
     <row r="2549">
@@ -25917,7 +25917,7 @@
         </is>
       </c>
       <c r="B2549" t="n">
-        <v>178.3723995433576</v>
+        <v>227.3204294063647</v>
       </c>
     </row>
     <row r="2550">
@@ -25927,7 +25927,7 @@
         </is>
       </c>
       <c r="B2550" t="n">
-        <v>166.686696961225</v>
+        <v>216.2778360495928</v>
       </c>
     </row>
     <row r="2551">
@@ -25937,7 +25937,7 @@
         </is>
       </c>
       <c r="B2551" t="n">
-        <v>168.0946864617714</v>
+        <v>218.5417524003028</v>
       </c>
     </row>
     <row r="2552">
@@ -25947,7 +25947,7 @@
         </is>
       </c>
       <c r="B2552" t="n">
-        <v>170.8403232379875</v>
+        <v>220.944620209384</v>
       </c>
     </row>
     <row r="2553">
@@ -25957,7 +25957,7 @@
         </is>
       </c>
       <c r="B2553" t="n">
-        <v>188.3711871932212</v>
+        <v>239.1149833511873</v>
       </c>
     </row>
     <row r="2554">
@@ -25967,7 +25967,7 @@
         </is>
       </c>
       <c r="B2554" t="n">
-        <v>201.4255056047576</v>
+        <v>254.0184772861847</v>
       </c>
     </row>
     <row r="2555">
@@ -25977,7 +25977,7 @@
         </is>
       </c>
       <c r="B2555" t="n">
-        <v>204.1449078855955</v>
+        <v>259.0126902512744</v>
       </c>
     </row>
     <row r="2556">
@@ -25987,7 +25987,7 @@
         </is>
       </c>
       <c r="B2556" t="n">
-        <v>212.0965994935095</v>
+        <v>268.218079341562</v>
       </c>
     </row>
     <row r="2557">
@@ -25997,7 +25997,7 @@
         </is>
       </c>
       <c r="B2557" t="n">
-        <v>186.7891580217288</v>
+        <v>245.8536554282476</v>
       </c>
     </row>
     <row r="2558">
@@ -26007,7 +26007,7 @@
         </is>
       </c>
       <c r="B2558" t="n">
-        <v>197.6900342079333</v>
+        <v>257.1889844703137</v>
       </c>
     </row>
     <row r="2559">
@@ -26017,7 +26017,7 @@
         </is>
       </c>
       <c r="B2559" t="n">
-        <v>184.2225239976935</v>
+        <v>243.7461311970016</v>
       </c>
     </row>
     <row r="2560">
@@ -26027,7 +26027,7 @@
         </is>
       </c>
       <c r="B2560" t="n">
-        <v>201.0042933359723</v>
+        <v>257.8008313367637</v>
       </c>
     </row>
     <row r="2561">
@@ -26037,7 +26037,7 @@
         </is>
       </c>
       <c r="B2561" t="n">
-        <v>166.9196303922364</v>
+        <v>225.4229095099073</v>
       </c>
     </row>
     <row r="2562">
@@ -26047,7 +26047,7 @@
         </is>
       </c>
       <c r="B2562" t="n">
-        <v>179.6470636065204</v>
+        <v>236.0410826884768</v>
       </c>
     </row>
     <row r="2563">
@@ -26057,7 +26057,7 @@
         </is>
       </c>
       <c r="B2563" t="n">
-        <v>192.4130660003751</v>
+        <v>247.9870358004875</v>
       </c>
     </row>
     <row r="2564">
@@ -26067,7 +26067,7 @@
         </is>
       </c>
       <c r="B2564" t="n">
-        <v>179.5247025552102</v>
+        <v>234.5081033217737</v>
       </c>
     </row>
     <row r="2565">
@@ -26077,7 +26077,7 @@
         </is>
       </c>
       <c r="B2565" t="n">
-        <v>172.8560997967857</v>
+        <v>227.9375097358215</v>
       </c>
     </row>
     <row r="2566">
@@ -26087,7 +26087,7 @@
         </is>
       </c>
       <c r="B2566" t="n">
-        <v>163.3101563381932</v>
+        <v>218.2483332396508</v>
       </c>
     </row>
     <row r="2567">
@@ -26097,7 +26097,7 @@
         </is>
       </c>
       <c r="B2567" t="n">
-        <v>159.474650704341</v>
+        <v>211.8141059156437</v>
       </c>
     </row>
     <row r="2568">
@@ -26107,7 +26107,7 @@
         </is>
       </c>
       <c r="B2568" t="n">
-        <v>158.1062392012565</v>
+        <v>209.4925909616337</v>
       </c>
     </row>
     <row r="2569">
@@ -26127,7 +26127,7 @@
         </is>
       </c>
       <c r="B2570" t="n">
-        <v>14.98020538838503</v>
+        <v>89.41549194960857</v>
       </c>
     </row>
     <row r="2571">
@@ -26137,7 +26137,7 @@
         </is>
       </c>
       <c r="B2571" t="n">
-        <v>0</v>
+        <v>62.1848505706408</v>
       </c>
     </row>
     <row r="2572">
@@ -26147,7 +26147,7 @@
         </is>
       </c>
       <c r="B2572" t="n">
-        <v>14.62339476467993</v>
+        <v>87.79174107256985</v>
       </c>
     </row>
     <row r="2573">
@@ -26157,7 +26157,7 @@
         </is>
       </c>
       <c r="B2573" t="n">
-        <v>15.53592941511514</v>
+        <v>84.07879278084766</v>
       </c>
     </row>
     <row r="2574">
@@ -26167,7 +26167,7 @@
         </is>
       </c>
       <c r="B2574" t="n">
-        <v>72.12831299638772</v>
+        <v>143.0748898816649</v>
       </c>
     </row>
     <row r="2575">
@@ -26177,7 +26177,7 @@
         </is>
       </c>
       <c r="B2575" t="n">
-        <v>71.14088900126666</v>
+        <v>137.9744187432735</v>
       </c>
     </row>
     <row r="2576">
@@ -26187,7 +26187,7 @@
         </is>
       </c>
       <c r="B2576" t="n">
-        <v>136.2270073633968</v>
+        <v>207.9137770724736</v>
       </c>
     </row>
     <row r="2577">
@@ -26197,7 +26197,7 @@
         </is>
       </c>
       <c r="B2577" t="n">
-        <v>54.16084032308625</v>
+        <v>128.8642392881483</v>
       </c>
     </row>
     <row r="2578">
@@ -26207,7 +26207,7 @@
         </is>
       </c>
       <c r="B2578" t="n">
-        <v>84.5232667135346</v>
+        <v>177.2132757110199</v>
       </c>
     </row>
     <row r="2579">
@@ -26217,7 +26217,7 @@
         </is>
       </c>
       <c r="B2579" t="n">
-        <v>78.92238707288278</v>
+        <v>195.1899124173716</v>
       </c>
     </row>
     <row r="2580">
@@ -26227,7 +26227,7 @@
         </is>
       </c>
       <c r="B2580" t="n">
-        <v>74.8605576049063</v>
+        <v>230.2621516295663</v>
       </c>
     </row>
     <row r="2581">
@@ -26237,7 +26237,7 @@
         </is>
       </c>
       <c r="B2581" t="n">
-        <v>92.49825334531972</v>
+        <v>255.8389696536029</v>
       </c>
     </row>
     <row r="2582">
@@ -26247,7 +26247,7 @@
         </is>
       </c>
       <c r="B2582" t="n">
-        <v>33.3569331946123</v>
+        <v>196.8462252009369</v>
       </c>
     </row>
     <row r="2583">
@@ -26257,7 +26257,7 @@
         </is>
       </c>
       <c r="B2583" t="n">
-        <v>65.26138019488246</v>
+        <v>214.6502746838136</v>
       </c>
     </row>
     <row r="2584">
@@ -26267,7 +26267,7 @@
         </is>
       </c>
       <c r="B2584" t="n">
-        <v>58.30765870055448</v>
+        <v>219.4842797467869</v>
       </c>
     </row>
     <row r="2585">
@@ -26277,7 +26277,7 @@
         </is>
       </c>
       <c r="B2585" t="n">
-        <v>25.90111335553154</v>
+        <v>169.5733895500958</v>
       </c>
     </row>
     <row r="2586">
@@ -26287,7 +26287,7 @@
         </is>
       </c>
       <c r="B2586" t="n">
-        <v>0</v>
+        <v>108.3571617580804</v>
       </c>
     </row>
     <row r="2587">
@@ -26297,7 +26297,7 @@
         </is>
       </c>
       <c r="B2587" t="n">
-        <v>0</v>
+        <v>68.11106661082576</v>
       </c>
     </row>
     <row r="2588">
@@ -26307,7 +26307,7 @@
         </is>
       </c>
       <c r="B2588" t="n">
-        <v>0</v>
+        <v>43.727777051742</v>
       </c>
     </row>
     <row r="2589">
@@ -26317,7 +26317,7 @@
         </is>
       </c>
       <c r="B2589" t="n">
-        <v>0</v>
+        <v>40.43804658580047</v>
       </c>
     </row>
     <row r="2590">
@@ -26327,7 +26327,7 @@
         </is>
       </c>
       <c r="B2590" t="n">
-        <v>0</v>
+        <v>57.38311149111763</v>
       </c>
     </row>
     <row r="2591">
@@ -26337,7 +26337,7 @@
         </is>
       </c>
       <c r="B2591" t="n">
-        <v>0</v>
+        <v>75.32693790859562</v>
       </c>
     </row>
     <row r="2592">
